--- a/AutoMobChart1.0/truedata/day_schedules/4_Thursday_schedule.xlsx
+++ b/AutoMobChart1.0/truedata/day_schedules/4_Thursday_schedule.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM17"/>
+  <dimension ref="A1:BM21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -2489,7 +2489,7 @@
     <row r="8" ht="20" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EMPERUA, JUSTIN KYLE LAGAYAN</t>
+          <t>DELA CRUZ, EZECKIEL JOSE SARENAS</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -2517,89 +2517,89 @@
           <t> </t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>Math 21; MB 304</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>Math 21; MB 304</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>Math 21; MB 304</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>GE 161; MH 318-320</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>GE 161; MH 318-320</t>
-        </is>
-      </c>
-      <c r="L8" s="5" t="inlineStr">
-        <is>
-          <t>GE 161; MH 318-320</t>
+          <t>Math 21; MB 304</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t> </t>
         </is>
       </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
-          <t>GE 161; MH 318-320</t>
+          <t>Physics 71; NIP F209</t>
         </is>
       </c>
       <c r="N8" s="5" t="inlineStr">
         <is>
-          <t>GE 161; MH 318-320</t>
+          <t>Physics 71; NIP F209</t>
         </is>
       </c>
       <c r="O8" s="5" t="inlineStr">
         <is>
-          <t>GE 161; MH 318-320</t>
+          <t>Physics 71; NIP F209</t>
         </is>
       </c>
       <c r="P8" s="5" t="inlineStr">
         <is>
-          <t>GE 161; MH 318-320</t>
-        </is>
-      </c>
-      <c r="Q8" s="5" t="inlineStr">
-        <is>
-          <t>GE 161; MH 318-320</t>
+          <t>Physics 71; NIP F209</t>
+        </is>
+      </c>
+      <c r="Q8" s="4" t="inlineStr">
+        <is>
+          <t> </t>
         </is>
       </c>
       <c r="R8" s="5" t="inlineStr">
         <is>
-          <t>GE 161; MH 318-320</t>
+          <t>Philo 1; PH 222</t>
         </is>
       </c>
       <c r="S8" s="5" t="inlineStr">
         <is>
-          <t>GE 161; MH 318-320</t>
+          <t>Philo 1; PH 222</t>
         </is>
       </c>
       <c r="T8" s="5" t="inlineStr">
         <is>
-          <t>GE 161; MH 318-320</t>
+          <t>Philo 1; PH 222</t>
         </is>
       </c>
       <c r="U8" s="5" t="inlineStr">
         <is>
-          <t>GE 161; MH 318-320</t>
-        </is>
-      </c>
-      <c r="V8" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="W8" s="4" t="inlineStr">
-        <is>
-          <t> </t>
+          <t>Philo 1; PH 222</t>
+        </is>
+      </c>
+      <c r="V8" s="5" t="inlineStr">
+        <is>
+          <t>Philo 1; PH 222</t>
+        </is>
+      </c>
+      <c r="W8" s="5" t="inlineStr">
+        <is>
+          <t>Philo 1; PH 222</t>
         </is>
       </c>
       <c r="X8" s="4" t="inlineStr">
@@ -2632,24 +2632,24 @@
           <t> </t>
         </is>
       </c>
-      <c r="AD8" s="5" t="inlineStr">
-        <is>
-          <t>Math 23; TBA</t>
-        </is>
-      </c>
-      <c r="AE8" s="5" t="inlineStr">
-        <is>
-          <t>Math 23; TBA</t>
-        </is>
-      </c>
-      <c r="AF8" s="5" t="inlineStr">
-        <is>
-          <t>Math 23; TBA</t>
-        </is>
-      </c>
-      <c r="AG8" s="5" t="inlineStr">
-        <is>
-          <t>Math 23; TBA</t>
+      <c r="AD8" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AE8" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AF8" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AG8" s="4" t="inlineStr">
+        <is>
+          <t> </t>
         </is>
       </c>
       <c r="AH8" s="4" t="inlineStr">
@@ -2672,64 +2672,64 @@
           <t> </t>
         </is>
       </c>
-      <c r="AL8" s="5" t="inlineStr">
-        <is>
-          <t>GE 122; MH 416-418</t>
-        </is>
-      </c>
-      <c r="AM8" s="5" t="inlineStr">
-        <is>
-          <t>GE 122; MH 416-418</t>
-        </is>
-      </c>
-      <c r="AN8" s="5" t="inlineStr">
-        <is>
-          <t>GE 122; MH 416-418</t>
-        </is>
-      </c>
-      <c r="AO8" s="5" t="inlineStr">
-        <is>
-          <t>GE 122; MH 416-418</t>
-        </is>
-      </c>
-      <c r="AP8" s="5" t="inlineStr">
-        <is>
-          <t>GE 122; MH 416-418</t>
-        </is>
-      </c>
-      <c r="AQ8" s="5" t="inlineStr">
-        <is>
-          <t>GE 122; MH 416-418</t>
-        </is>
-      </c>
-      <c r="AR8" s="5" t="inlineStr">
-        <is>
-          <t>GE 122; MH 416-418</t>
-        </is>
-      </c>
-      <c r="AS8" s="5" t="inlineStr">
-        <is>
-          <t>GE 122; MH 416-418</t>
-        </is>
-      </c>
-      <c r="AT8" s="5" t="inlineStr">
-        <is>
-          <t>GE 122; MH 416-418</t>
-        </is>
-      </c>
-      <c r="AU8" s="5" t="inlineStr">
-        <is>
-          <t>GE 122; MH 416-418</t>
-        </is>
-      </c>
-      <c r="AV8" s="5" t="inlineStr">
-        <is>
-          <t>GE 122; MH 416-418</t>
-        </is>
-      </c>
-      <c r="AW8" s="5" t="inlineStr">
-        <is>
-          <t>GE 122; MH 416-418</t>
+      <c r="AL8" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AM8" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AN8" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AO8" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AP8" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AQ8" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AR8" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AS8" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AT8" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AU8" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AV8" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AW8" s="4" t="inlineStr">
+        <is>
+          <t> </t>
         </is>
       </c>
       <c r="AX8" s="4" t="inlineStr">
@@ -2816,7 +2816,7 @@
     <row r="9" ht="20" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FERNANDEZ, JAM BASA</t>
+          <t>EIMAN, GERTRO FELIX DUMARAOG</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -2869,29 +2869,29 @@
           <t> </t>
         </is>
       </c>
-      <c r="L9" s="5" t="inlineStr">
-        <is>
-          <t>Physics 107; NIP F202</t>
-        </is>
-      </c>
-      <c r="M9" s="5" t="inlineStr">
-        <is>
-          <t>Physics 107; NIP F202</t>
-        </is>
-      </c>
-      <c r="N9" s="5" t="inlineStr">
-        <is>
-          <t>Physics 107; NIP F202</t>
-        </is>
-      </c>
-      <c r="O9" s="5" t="inlineStr">
-        <is>
-          <t>Physics 107; NIP F202</t>
-        </is>
-      </c>
-      <c r="P9" s="5" t="inlineStr">
-        <is>
-          <t>Physics 107; NIP F202</t>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="O9" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="P9" s="4" t="inlineStr">
+        <is>
+          <t> </t>
         </is>
       </c>
       <c r="Q9" s="4" t="inlineStr">
@@ -2901,32 +2901,32 @@
       </c>
       <c r="R9" s="5" t="inlineStr">
         <is>
-          <t>Physics 116; NIP LP101</t>
+          <t>ARTS 1; TBA</t>
         </is>
       </c>
       <c r="S9" s="5" t="inlineStr">
         <is>
-          <t>Physics 116; NIP LP101</t>
+          <t>ARTS 1; TBA</t>
         </is>
       </c>
       <c r="T9" s="5" t="inlineStr">
         <is>
-          <t>Physics 116; NIP LP101</t>
+          <t>ARTS 1; TBA</t>
         </is>
       </c>
       <c r="U9" s="5" t="inlineStr">
         <is>
-          <t>Physics 116; NIP LP101</t>
+          <t>ARTS 1; TBA</t>
         </is>
       </c>
       <c r="V9" s="5" t="inlineStr">
         <is>
-          <t>Physics 116; NIP LP101</t>
-        </is>
-      </c>
-      <c r="W9" s="4" t="inlineStr">
-        <is>
-          <t> </t>
+          <t>ARTS 1; TBA</t>
+        </is>
+      </c>
+      <c r="W9" s="5" t="inlineStr">
+        <is>
+          <t>ARTS 1; TBA</t>
         </is>
       </c>
       <c r="X9" s="4" t="inlineStr">
@@ -2959,24 +2959,24 @@
           <t> </t>
         </is>
       </c>
-      <c r="AD9" s="5" t="inlineStr">
-        <is>
-          <t>Math 23; TBA</t>
-        </is>
-      </c>
-      <c r="AE9" s="5" t="inlineStr">
-        <is>
-          <t>Math 23; TBA</t>
-        </is>
-      </c>
-      <c r="AF9" s="5" t="inlineStr">
-        <is>
-          <t>Math 23; TBA</t>
-        </is>
-      </c>
-      <c r="AG9" s="5" t="inlineStr">
-        <is>
-          <t>Math 23; TBA</t>
+      <c r="AD9" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AE9" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AF9" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AG9" s="4" t="inlineStr">
+        <is>
+          <t> </t>
         </is>
       </c>
       <c r="AH9" s="4" t="inlineStr">
@@ -3019,34 +3019,34 @@
           <t> </t>
         </is>
       </c>
-      <c r="AP9" s="5" t="inlineStr">
-        <is>
-          <t>Math 122; MB 120</t>
-        </is>
-      </c>
-      <c r="AQ9" s="5" t="inlineStr">
-        <is>
-          <t>Math 122; MB 120</t>
-        </is>
-      </c>
-      <c r="AR9" s="5" t="inlineStr">
-        <is>
-          <t>Math 122; MB 120</t>
-        </is>
-      </c>
-      <c r="AS9" s="5" t="inlineStr">
-        <is>
-          <t>Math 122; MB 120</t>
-        </is>
-      </c>
-      <c r="AT9" s="5" t="inlineStr">
-        <is>
-          <t>Math 122; MB 120</t>
-        </is>
-      </c>
-      <c r="AU9" s="5" t="inlineStr">
-        <is>
-          <t>Math 122; MB 120</t>
+      <c r="AP9" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AQ9" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AR9" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AS9" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AT9" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AU9" s="4" t="inlineStr">
+        <is>
+          <t> </t>
         </is>
       </c>
       <c r="AV9" s="4" t="inlineStr">
@@ -3143,7 +3143,7 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GAVILAN, SEAN CEDRICK JACOBE</t>
+          <t>EMPERUA, JUSTIN KYLE LAGAYAN</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -3186,64 +3186,64 @@
           <t> </t>
         </is>
       </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="L10" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="M10" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="N10" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="O10" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="P10" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="Q10" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="R10" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="S10" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="T10" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="U10" s="4" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>GE 161; MH 318-320</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>GE 161; MH 318-320</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>GE 161; MH 318-320</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="inlineStr">
+        <is>
+          <t>GE 161; MH 318-320</t>
+        </is>
+      </c>
+      <c r="N10" s="5" t="inlineStr">
+        <is>
+          <t>GE 161; MH 318-320</t>
+        </is>
+      </c>
+      <c r="O10" s="5" t="inlineStr">
+        <is>
+          <t>GE 161; MH 318-320</t>
+        </is>
+      </c>
+      <c r="P10" s="5" t="inlineStr">
+        <is>
+          <t>GE 161; MH 318-320</t>
+        </is>
+      </c>
+      <c r="Q10" s="5" t="inlineStr">
+        <is>
+          <t>GE 161; MH 318-320</t>
+        </is>
+      </c>
+      <c r="R10" s="5" t="inlineStr">
+        <is>
+          <t>GE 161; MH 318-320</t>
+        </is>
+      </c>
+      <c r="S10" s="5" t="inlineStr">
+        <is>
+          <t>GE 161; MH 318-320</t>
+        </is>
+      </c>
+      <c r="T10" s="5" t="inlineStr">
+        <is>
+          <t>GE 161; MH 318-320</t>
+        </is>
+      </c>
+      <c r="U10" s="5" t="inlineStr">
+        <is>
+          <t>GE 161; MH 318-320</t>
         </is>
       </c>
       <c r="V10" s="4" t="inlineStr">
@@ -3288,32 +3288,32 @@
       </c>
       <c r="AD10" s="5" t="inlineStr">
         <is>
-          <t>Archaeo 2; Classroom B</t>
+          <t>Math 23; TBA</t>
         </is>
       </c>
       <c r="AE10" s="5" t="inlineStr">
         <is>
-          <t>Archaeo 2; Classroom B</t>
+          <t>Math 23; TBA</t>
         </is>
       </c>
       <c r="AF10" s="5" t="inlineStr">
         <is>
-          <t>Archaeo 2; Classroom B</t>
+          <t>Math 23; TBA</t>
         </is>
       </c>
       <c r="AG10" s="5" t="inlineStr">
         <is>
-          <t>Archaeo 2; Classroom B</t>
-        </is>
-      </c>
-      <c r="AH10" s="5" t="inlineStr">
-        <is>
-          <t>Archaeo 2; Classroom B</t>
-        </is>
-      </c>
-      <c r="AI10" s="5" t="inlineStr">
-        <is>
-          <t>Archaeo 2; Classroom B</t>
+          <t>Math 23; TBA</t>
+        </is>
+      </c>
+      <c r="AH10" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AI10" s="4" t="inlineStr">
+        <is>
+          <t> </t>
         </is>
       </c>
       <c r="AJ10" s="4" t="inlineStr">
@@ -3326,64 +3326,64 @@
           <t> </t>
         </is>
       </c>
-      <c r="AL10" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AM10" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AN10" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AO10" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AP10" s="4" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="AL10" s="5" t="inlineStr">
+        <is>
+          <t>GE 122; MH 416-418</t>
+        </is>
+      </c>
+      <c r="AM10" s="5" t="inlineStr">
+        <is>
+          <t>GE 122; MH 416-418</t>
+        </is>
+      </c>
+      <c r="AN10" s="5" t="inlineStr">
+        <is>
+          <t>GE 122; MH 416-418</t>
+        </is>
+      </c>
+      <c r="AO10" s="5" t="inlineStr">
+        <is>
+          <t>GE 122; MH 416-418</t>
+        </is>
+      </c>
+      <c r="AP10" s="5" t="inlineStr">
+        <is>
+          <t>GE 122; MH 416-418</t>
         </is>
       </c>
       <c r="AQ10" s="5" t="inlineStr">
         <is>
-          <t>Math 21; MB 307</t>
+          <t>GE 122; MH 416-418</t>
         </is>
       </c>
       <c r="AR10" s="5" t="inlineStr">
         <is>
-          <t>Math 21; MB 307</t>
+          <t>GE 122; MH 416-418</t>
         </is>
       </c>
       <c r="AS10" s="5" t="inlineStr">
         <is>
-          <t>Math 21; MB 307</t>
+          <t>GE 122; MH 416-418</t>
         </is>
       </c>
       <c r="AT10" s="5" t="inlineStr">
         <is>
-          <t>Math 21; MB 307</t>
-        </is>
-      </c>
-      <c r="AU10" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AV10" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AW10" s="4" t="inlineStr">
-        <is>
-          <t> </t>
+          <t>GE 122; MH 416-418</t>
+        </is>
+      </c>
+      <c r="AU10" s="5" t="inlineStr">
+        <is>
+          <t>GE 122; MH 416-418</t>
+        </is>
+      </c>
+      <c r="AV10" s="5" t="inlineStr">
+        <is>
+          <t>GE 122; MH 416-418</t>
+        </is>
+      </c>
+      <c r="AW10" s="5" t="inlineStr">
+        <is>
+          <t>GE 122; MH 416-418</t>
         </is>
       </c>
       <c r="AX10" s="4" t="inlineStr">
@@ -3470,7 +3470,7 @@
     <row r="11" ht="20" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GOCHUICO, AKHILLIS DELA CRUZ</t>
+          <t>FERNANDEZ, JAM BASA</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -3523,29 +3523,29 @@
           <t> </t>
         </is>
       </c>
-      <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="M11" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="N11" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="O11" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="P11" s="4" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>Physics 107; NIP F202</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="inlineStr">
+        <is>
+          <t>Physics 107; NIP F202</t>
+        </is>
+      </c>
+      <c r="N11" s="5" t="inlineStr">
+        <is>
+          <t>Physics 107; NIP F202</t>
+        </is>
+      </c>
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>Physics 107; NIP F202</t>
+        </is>
+      </c>
+      <c r="P11" s="5" t="inlineStr">
+        <is>
+          <t>Physics 107; NIP F202</t>
         </is>
       </c>
       <c r="Q11" s="4" t="inlineStr">
@@ -3555,152 +3555,152 @@
       </c>
       <c r="R11" s="5" t="inlineStr">
         <is>
-          <t>Acctg 1; BA 208</t>
+          <t>Physics 116; NIP LP101</t>
         </is>
       </c>
       <c r="S11" s="5" t="inlineStr">
         <is>
-          <t>Acctg 1; BA 208</t>
+          <t>Physics 116; NIP LP101</t>
         </is>
       </c>
       <c r="T11" s="5" t="inlineStr">
         <is>
-          <t>Acctg 1; BA 208</t>
+          <t>Physics 116; NIP LP101</t>
         </is>
       </c>
       <c r="U11" s="5" t="inlineStr">
         <is>
-          <t>Acctg 1; BA 208</t>
+          <t>Physics 116; NIP LP101</t>
         </is>
       </c>
       <c r="V11" s="5" t="inlineStr">
         <is>
-          <t>Acctg 1; BA 208</t>
-        </is>
-      </c>
-      <c r="W11" s="5" t="inlineStr">
-        <is>
-          <t>Acctg 1; BA 208</t>
-        </is>
-      </c>
-      <c r="X11" s="5" t="inlineStr">
-        <is>
-          <t>IE 27; IE-ME 111</t>
-        </is>
-      </c>
-      <c r="Y11" s="5" t="inlineStr">
-        <is>
-          <t>IE 27; IE-ME 111</t>
-        </is>
-      </c>
-      <c r="Z11" s="5" t="inlineStr">
-        <is>
-          <t>IE 27; IE-ME 111</t>
-        </is>
-      </c>
-      <c r="AA11" s="5" t="inlineStr">
-        <is>
-          <t>IE 27; IE-ME 111</t>
-        </is>
-      </c>
-      <c r="AB11" s="5" t="inlineStr">
-        <is>
-          <t>IE 27; IE-ME 111</t>
-        </is>
-      </c>
-      <c r="AC11" s="5" t="inlineStr">
-        <is>
-          <t>IE 27; IE-ME 111</t>
+          <t>Physics 116; NIP LP101</t>
+        </is>
+      </c>
+      <c r="W11" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="X11" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="Y11" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="Z11" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AA11" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AB11" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AC11" s="4" t="inlineStr">
+        <is>
+          <t> </t>
         </is>
       </c>
       <c r="AD11" s="5" t="inlineStr">
         <is>
-          <t>IE 21; MH 417-419</t>
+          <t>Math 23; TBA</t>
         </is>
       </c>
       <c r="AE11" s="5" t="inlineStr">
         <is>
-          <t>IE 21; MH 417-419</t>
+          <t>Math 23; TBA</t>
         </is>
       </c>
       <c r="AF11" s="5" t="inlineStr">
         <is>
-          <t>IE 21; MH 417-419</t>
+          <t>Math 23; TBA</t>
         </is>
       </c>
       <c r="AG11" s="5" t="inlineStr">
         <is>
-          <t>IE 21; MH 417-419</t>
-        </is>
-      </c>
-      <c r="AH11" s="5" t="inlineStr">
-        <is>
-          <t>IE 21; MH 417-419</t>
-        </is>
-      </c>
-      <c r="AI11" s="5" t="inlineStr">
-        <is>
-          <t>IE 21; MH 417-419</t>
-        </is>
-      </c>
-      <c r="AJ11" s="5" t="inlineStr">
-        <is>
-          <t>IE 40; TBA</t>
-        </is>
-      </c>
-      <c r="AK11" s="5" t="inlineStr">
-        <is>
-          <t>IE 40; TBA</t>
-        </is>
-      </c>
-      <c r="AL11" s="5" t="inlineStr">
-        <is>
-          <t>IE 40; TBA</t>
-        </is>
-      </c>
-      <c r="AM11" s="5" t="inlineStr">
-        <is>
-          <t>IE 40; TBA</t>
-        </is>
-      </c>
-      <c r="AN11" s="5" t="inlineStr">
-        <is>
-          <t>IE 40; TBA</t>
-        </is>
-      </c>
-      <c r="AO11" s="5" t="inlineStr">
-        <is>
-          <t>IE 40; TBA</t>
-        </is>
-      </c>
-      <c r="AP11" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AQ11" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AR11" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AS11" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AT11" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AU11" s="4" t="inlineStr">
-        <is>
-          <t> </t>
+          <t>Math 23; TBA</t>
+        </is>
+      </c>
+      <c r="AH11" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AI11" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AJ11" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AK11" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AL11" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AM11" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AN11" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AO11" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AP11" s="5" t="inlineStr">
+        <is>
+          <t>Math 122; MB 120</t>
+        </is>
+      </c>
+      <c r="AQ11" s="5" t="inlineStr">
+        <is>
+          <t>Math 122; MB 120</t>
+        </is>
+      </c>
+      <c r="AR11" s="5" t="inlineStr">
+        <is>
+          <t>Math 122; MB 120</t>
+        </is>
+      </c>
+      <c r="AS11" s="5" t="inlineStr">
+        <is>
+          <t>Math 122; MB 120</t>
+        </is>
+      </c>
+      <c r="AT11" s="5" t="inlineStr">
+        <is>
+          <t>Math 122; MB 120</t>
+        </is>
+      </c>
+      <c r="AU11" s="5" t="inlineStr">
+        <is>
+          <t>Math 122; MB 120</t>
         </is>
       </c>
       <c r="AV11" s="4" t="inlineStr">
@@ -3797,7 +3797,7 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IBAY, DOMINIC JOB MORALES</t>
+          <t>GAVILAN, SEAN CEDRICK JACOBE</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -3850,184 +3850,184 @@
           <t> </t>
         </is>
       </c>
-      <c r="L12" s="5" t="inlineStr">
-        <is>
-          <t>Physics 142; NIP R109</t>
-        </is>
-      </c>
-      <c r="M12" s="5" t="inlineStr">
-        <is>
-          <t>Physics 142; NIP R109</t>
-        </is>
-      </c>
-      <c r="N12" s="5" t="inlineStr">
-        <is>
-          <t>Physics 142; NIP R109</t>
-        </is>
-      </c>
-      <c r="O12" s="5" t="inlineStr">
-        <is>
-          <t>Physics 142; NIP R109</t>
-        </is>
-      </c>
-      <c r="P12" s="5" t="inlineStr">
-        <is>
-          <t>Physics 142; NIP R109</t>
-        </is>
-      </c>
-      <c r="Q12" s="5" t="inlineStr">
-        <is>
-          <t>Physics 142; NIP R109</t>
-        </is>
-      </c>
-      <c r="R12" s="5" t="inlineStr">
-        <is>
-          <t>Physics 170; NIP F202</t>
-        </is>
-      </c>
-      <c r="S12" s="5" t="inlineStr">
-        <is>
-          <t>Physics 170; NIP F202</t>
-        </is>
-      </c>
-      <c r="T12" s="5" t="inlineStr">
-        <is>
-          <t>Physics 170; NIP F202</t>
-        </is>
-      </c>
-      <c r="U12" s="5" t="inlineStr">
-        <is>
-          <t>Physics 170; NIP F202</t>
-        </is>
-      </c>
-      <c r="V12" s="5" t="inlineStr">
-        <is>
-          <t>Physics 170; NIP F202</t>
-        </is>
-      </c>
-      <c r="W12" s="5" t="inlineStr">
-        <is>
-          <t>Physics 170; NIP F202</t>
-        </is>
-      </c>
-      <c r="X12" s="5" t="inlineStr">
-        <is>
-          <t>App Physics 167; NIP R109</t>
-        </is>
-      </c>
-      <c r="Y12" s="5" t="inlineStr">
-        <is>
-          <t>App Physics 167; NIP R109</t>
-        </is>
-      </c>
-      <c r="Z12" s="5" t="inlineStr">
-        <is>
-          <t>App Physics 167; NIP R109</t>
-        </is>
-      </c>
-      <c r="AA12" s="5" t="inlineStr">
-        <is>
-          <t>App Physics 167; NIP R109</t>
-        </is>
-      </c>
-      <c r="AB12" s="5" t="inlineStr">
-        <is>
-          <t>App Physics 167; NIP R109</t>
-        </is>
-      </c>
-      <c r="AC12" s="5" t="inlineStr">
-        <is>
-          <t>App Physics 167; NIP R109</t>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="O12" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="P12" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="Q12" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="R12" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="S12" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="T12" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="U12" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="V12" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="W12" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="X12" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="Y12" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="Z12" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AA12" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AB12" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AC12" s="4" t="inlineStr">
+        <is>
+          <t> </t>
         </is>
       </c>
       <c r="AD12" s="5" t="inlineStr">
         <is>
-          <t>Physics 192; TBA</t>
+          <t>Archaeo 2; Classroom B</t>
         </is>
       </c>
       <c r="AE12" s="5" t="inlineStr">
         <is>
-          <t>Physics 192; TBA</t>
+          <t>Archaeo 2; Classroom B</t>
         </is>
       </c>
       <c r="AF12" s="5" t="inlineStr">
         <is>
-          <t>Physics 192; TBA</t>
+          <t>Archaeo 2; Classroom B</t>
         </is>
       </c>
       <c r="AG12" s="5" t="inlineStr">
         <is>
-          <t>Physics 192; TBA</t>
+          <t>Archaeo 2; Classroom B</t>
         </is>
       </c>
       <c r="AH12" s="5" t="inlineStr">
         <is>
-          <t>Physics 192; TBA</t>
+          <t>Archaeo 2; Classroom B</t>
         </is>
       </c>
       <c r="AI12" s="5" t="inlineStr">
         <is>
-          <t>Physics 192; TBA</t>
-        </is>
-      </c>
-      <c r="AJ12" s="5" t="inlineStr">
-        <is>
-          <t>Physics 192; TBA</t>
-        </is>
-      </c>
-      <c r="AK12" s="5" t="inlineStr">
-        <is>
-          <t>Physics 192; TBA</t>
-        </is>
-      </c>
-      <c r="AL12" s="5" t="inlineStr">
-        <is>
-          <t>Physics 192; TBA</t>
-        </is>
-      </c>
-      <c r="AM12" s="5" t="inlineStr">
-        <is>
-          <t>Physics 192; TBA</t>
-        </is>
-      </c>
-      <c r="AN12" s="5" t="inlineStr">
-        <is>
-          <t>Physics 192; TBA</t>
-        </is>
-      </c>
-      <c r="AO12" s="5" t="inlineStr">
-        <is>
-          <t>Physics 192; TBA</t>
-        </is>
-      </c>
-      <c r="AP12" s="5" t="inlineStr">
-        <is>
-          <t>App Physics 184; NIP R201</t>
+          <t>Archaeo 2; Classroom B</t>
+        </is>
+      </c>
+      <c r="AJ12" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AK12" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AL12" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AM12" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AN12" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AO12" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AP12" s="4" t="inlineStr">
+        <is>
+          <t> </t>
         </is>
       </c>
       <c r="AQ12" s="5" t="inlineStr">
         <is>
-          <t>App Physics 184; NIP R201</t>
+          <t>Math 21; MB 307</t>
         </is>
       </c>
       <c r="AR12" s="5" t="inlineStr">
         <is>
-          <t>App Physics 184; NIP R201</t>
+          <t>Math 21; MB 307</t>
         </is>
       </c>
       <c r="AS12" s="5" t="inlineStr">
         <is>
-          <t>App Physics 184; NIP R201</t>
+          <t>Math 21; MB 307</t>
         </is>
       </c>
       <c r="AT12" s="5" t="inlineStr">
         <is>
-          <t>App Physics 184; NIP R201</t>
-        </is>
-      </c>
-      <c r="AU12" s="5" t="inlineStr">
-        <is>
-          <t>App Physics 184; NIP R201</t>
+          <t>Math 21; MB 307</t>
+        </is>
+      </c>
+      <c r="AU12" s="4" t="inlineStr">
+        <is>
+          <t> </t>
         </is>
       </c>
       <c r="AV12" s="4" t="inlineStr">
@@ -4124,7 +4124,7 @@
     <row r="13" ht="20" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>JUAN, VERCIL ACUSAR</t>
+          <t>GOCHUICO, AKHILLIS DELA CRUZ</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -4177,154 +4177,154 @@
           <t> </t>
         </is>
       </c>
-      <c r="L13" s="5" t="inlineStr">
-        <is>
-          <t>Physics 142; NIP R109</t>
-        </is>
-      </c>
-      <c r="M13" s="5" t="inlineStr">
-        <is>
-          <t>Physics 142; NIP R109</t>
-        </is>
-      </c>
-      <c r="N13" s="5" t="inlineStr">
-        <is>
-          <t>Physics 142; NIP R109</t>
-        </is>
-      </c>
-      <c r="O13" s="5" t="inlineStr">
-        <is>
-          <t>Physics 142; NIP R109</t>
-        </is>
-      </c>
-      <c r="P13" s="5" t="inlineStr">
-        <is>
-          <t>Physics 142; NIP R109</t>
-        </is>
-      </c>
-      <c r="Q13" s="5" t="inlineStr">
-        <is>
-          <t>Physics 142; NIP R109</t>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="M13" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="O13" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="P13" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="Q13" s="4" t="inlineStr">
+        <is>
+          <t> </t>
         </is>
       </c>
       <c r="R13" s="5" t="inlineStr">
         <is>
-          <t>Physics 170; NIP R201</t>
+          <t>Acctg 1; BA 208</t>
         </is>
       </c>
       <c r="S13" s="5" t="inlineStr">
         <is>
-          <t>Physics 170; NIP R201</t>
+          <t>Acctg 1; BA 208</t>
         </is>
       </c>
       <c r="T13" s="5" t="inlineStr">
         <is>
-          <t>Physics 170; NIP R201</t>
+          <t>Acctg 1; BA 208</t>
         </is>
       </c>
       <c r="U13" s="5" t="inlineStr">
         <is>
-          <t>Physics 170; NIP R201</t>
+          <t>Acctg 1; BA 208</t>
         </is>
       </c>
       <c r="V13" s="5" t="inlineStr">
         <is>
-          <t>Physics 170; NIP R201</t>
+          <t>Acctg 1; BA 208</t>
         </is>
       </c>
       <c r="W13" s="5" t="inlineStr">
         <is>
-          <t>Physics 170; NIP R201</t>
-        </is>
-      </c>
-      <c r="X13" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="Y13" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="Z13" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AA13" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AB13" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AC13" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AD13" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AE13" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AF13" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AG13" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AH13" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AI13" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AJ13" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AK13" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AL13" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AM13" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AN13" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AO13" s="4" t="inlineStr">
-        <is>
-          <t> </t>
+          <t>Acctg 1; BA 208</t>
+        </is>
+      </c>
+      <c r="X13" s="5" t="inlineStr">
+        <is>
+          <t>IE 27; IE-ME 111</t>
+        </is>
+      </c>
+      <c r="Y13" s="5" t="inlineStr">
+        <is>
+          <t>IE 27; IE-ME 111</t>
+        </is>
+      </c>
+      <c r="Z13" s="5" t="inlineStr">
+        <is>
+          <t>IE 27; IE-ME 111</t>
+        </is>
+      </c>
+      <c r="AA13" s="5" t="inlineStr">
+        <is>
+          <t>IE 27; IE-ME 111</t>
+        </is>
+      </c>
+      <c r="AB13" s="5" t="inlineStr">
+        <is>
+          <t>IE 27; IE-ME 111</t>
+        </is>
+      </c>
+      <c r="AC13" s="5" t="inlineStr">
+        <is>
+          <t>IE 27; IE-ME 111</t>
+        </is>
+      </c>
+      <c r="AD13" s="5" t="inlineStr">
+        <is>
+          <t>IE 21; MH 417-419</t>
+        </is>
+      </c>
+      <c r="AE13" s="5" t="inlineStr">
+        <is>
+          <t>IE 21; MH 417-419</t>
+        </is>
+      </c>
+      <c r="AF13" s="5" t="inlineStr">
+        <is>
+          <t>IE 21; MH 417-419</t>
+        </is>
+      </c>
+      <c r="AG13" s="5" t="inlineStr">
+        <is>
+          <t>IE 21; MH 417-419</t>
+        </is>
+      </c>
+      <c r="AH13" s="5" t="inlineStr">
+        <is>
+          <t>IE 21; MH 417-419</t>
+        </is>
+      </c>
+      <c r="AI13" s="5" t="inlineStr">
+        <is>
+          <t>IE 21; MH 417-419</t>
+        </is>
+      </c>
+      <c r="AJ13" s="5" t="inlineStr">
+        <is>
+          <t>IE 40; TBA</t>
+        </is>
+      </c>
+      <c r="AK13" s="5" t="inlineStr">
+        <is>
+          <t>IE 40; TBA</t>
+        </is>
+      </c>
+      <c r="AL13" s="5" t="inlineStr">
+        <is>
+          <t>IE 40; TBA</t>
+        </is>
+      </c>
+      <c r="AM13" s="5" t="inlineStr">
+        <is>
+          <t>IE 40; TBA</t>
+        </is>
+      </c>
+      <c r="AN13" s="5" t="inlineStr">
+        <is>
+          <t>IE 40; TBA</t>
+        </is>
+      </c>
+      <c r="AO13" s="5" t="inlineStr">
+        <is>
+          <t>IE 40; TBA</t>
         </is>
       </c>
       <c r="AP13" s="4" t="inlineStr">
@@ -4451,7 +4451,7 @@
     <row r="14" ht="20" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MARASIGAN, MIKE ANTHONY JOSON</t>
+          <t>IBAY, DOMINIC JOB MORALES</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -4504,184 +4504,184 @@
           <t> </t>
         </is>
       </c>
-      <c r="L14" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="M14" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="N14" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="O14" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="P14" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="Q14" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="R14" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="S14" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="T14" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="U14" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="V14" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="W14" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="X14" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="Y14" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="Z14" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AA14" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AB14" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AC14" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AD14" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AE14" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AF14" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AG14" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AH14" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AI14" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AJ14" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AK14" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AL14" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AM14" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AN14" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AO14" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AP14" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AQ14" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AR14" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AS14" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AT14" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AU14" s="4" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>Physics 142; NIP R109</t>
+        </is>
+      </c>
+      <c r="M14" s="5" t="inlineStr">
+        <is>
+          <t>Physics 142; NIP R109</t>
+        </is>
+      </c>
+      <c r="N14" s="5" t="inlineStr">
+        <is>
+          <t>Physics 142; NIP R109</t>
+        </is>
+      </c>
+      <c r="O14" s="5" t="inlineStr">
+        <is>
+          <t>Physics 142; NIP R109</t>
+        </is>
+      </c>
+      <c r="P14" s="5" t="inlineStr">
+        <is>
+          <t>Physics 142; NIP R109</t>
+        </is>
+      </c>
+      <c r="Q14" s="5" t="inlineStr">
+        <is>
+          <t>Physics 142; NIP R109</t>
+        </is>
+      </c>
+      <c r="R14" s="5" t="inlineStr">
+        <is>
+          <t>Physics 170; NIP F202</t>
+        </is>
+      </c>
+      <c r="S14" s="5" t="inlineStr">
+        <is>
+          <t>Physics 170; NIP F202</t>
+        </is>
+      </c>
+      <c r="T14" s="5" t="inlineStr">
+        <is>
+          <t>Physics 170; NIP F202</t>
+        </is>
+      </c>
+      <c r="U14" s="5" t="inlineStr">
+        <is>
+          <t>Physics 170; NIP F202</t>
+        </is>
+      </c>
+      <c r="V14" s="5" t="inlineStr">
+        <is>
+          <t>Physics 170; NIP F202</t>
+        </is>
+      </c>
+      <c r="W14" s="5" t="inlineStr">
+        <is>
+          <t>Physics 170; NIP F202</t>
+        </is>
+      </c>
+      <c r="X14" s="5" t="inlineStr">
+        <is>
+          <t>App Physics 167; NIP R109</t>
+        </is>
+      </c>
+      <c r="Y14" s="5" t="inlineStr">
+        <is>
+          <t>App Physics 167; NIP R109</t>
+        </is>
+      </c>
+      <c r="Z14" s="5" t="inlineStr">
+        <is>
+          <t>App Physics 167; NIP R109</t>
+        </is>
+      </c>
+      <c r="AA14" s="5" t="inlineStr">
+        <is>
+          <t>App Physics 167; NIP R109</t>
+        </is>
+      </c>
+      <c r="AB14" s="5" t="inlineStr">
+        <is>
+          <t>App Physics 167; NIP R109</t>
+        </is>
+      </c>
+      <c r="AC14" s="5" t="inlineStr">
+        <is>
+          <t>App Physics 167; NIP R109</t>
+        </is>
+      </c>
+      <c r="AD14" s="5" t="inlineStr">
+        <is>
+          <t>Physics 192; TBA</t>
+        </is>
+      </c>
+      <c r="AE14" s="5" t="inlineStr">
+        <is>
+          <t>Physics 192; TBA</t>
+        </is>
+      </c>
+      <c r="AF14" s="5" t="inlineStr">
+        <is>
+          <t>Physics 192; TBA</t>
+        </is>
+      </c>
+      <c r="AG14" s="5" t="inlineStr">
+        <is>
+          <t>Physics 192; TBA</t>
+        </is>
+      </c>
+      <c r="AH14" s="5" t="inlineStr">
+        <is>
+          <t>Physics 192; TBA</t>
+        </is>
+      </c>
+      <c r="AI14" s="5" t="inlineStr">
+        <is>
+          <t>Physics 192; TBA</t>
+        </is>
+      </c>
+      <c r="AJ14" s="5" t="inlineStr">
+        <is>
+          <t>Physics 192; TBA</t>
+        </is>
+      </c>
+      <c r="AK14" s="5" t="inlineStr">
+        <is>
+          <t>Physics 192; TBA</t>
+        </is>
+      </c>
+      <c r="AL14" s="5" t="inlineStr">
+        <is>
+          <t>Physics 192; TBA</t>
+        </is>
+      </c>
+      <c r="AM14" s="5" t="inlineStr">
+        <is>
+          <t>Physics 192; TBA</t>
+        </is>
+      </c>
+      <c r="AN14" s="5" t="inlineStr">
+        <is>
+          <t>Physics 192; TBA</t>
+        </is>
+      </c>
+      <c r="AO14" s="5" t="inlineStr">
+        <is>
+          <t>Physics 192; TBA</t>
+        </is>
+      </c>
+      <c r="AP14" s="5" t="inlineStr">
+        <is>
+          <t>App Physics 184; NIP R201</t>
+        </is>
+      </c>
+      <c r="AQ14" s="5" t="inlineStr">
+        <is>
+          <t>App Physics 184; NIP R201</t>
+        </is>
+      </c>
+      <c r="AR14" s="5" t="inlineStr">
+        <is>
+          <t>App Physics 184; NIP R201</t>
+        </is>
+      </c>
+      <c r="AS14" s="5" t="inlineStr">
+        <is>
+          <t>App Physics 184; NIP R201</t>
+        </is>
+      </c>
+      <c r="AT14" s="5" t="inlineStr">
+        <is>
+          <t>App Physics 184; NIP R201</t>
+        </is>
+      </c>
+      <c r="AU14" s="5" t="inlineStr">
+        <is>
+          <t>App Physics 184; NIP R201</t>
         </is>
       </c>
       <c r="AV14" s="4" t="inlineStr">
@@ -4694,44 +4694,44 @@
           <t> </t>
         </is>
       </c>
-      <c r="AX14" s="5" t="inlineStr">
-        <is>
-          <t>Law 103; LAW 221</t>
-        </is>
-      </c>
-      <c r="AY14" s="5" t="inlineStr">
-        <is>
-          <t>Law 103; LAW 221</t>
-        </is>
-      </c>
-      <c r="AZ14" s="5" t="inlineStr">
-        <is>
-          <t>Law 103; LAW 221</t>
-        </is>
-      </c>
-      <c r="BA14" s="5" t="inlineStr">
-        <is>
-          <t>Law 103; LAW 221</t>
-        </is>
-      </c>
-      <c r="BB14" s="5" t="inlineStr">
-        <is>
-          <t>Law 103; LAW 221</t>
-        </is>
-      </c>
-      <c r="BC14" s="5" t="inlineStr">
-        <is>
-          <t>Law 103; LAW 221</t>
-        </is>
-      </c>
-      <c r="BD14" s="5" t="inlineStr">
-        <is>
-          <t>Law 103; LAW 221</t>
-        </is>
-      </c>
-      <c r="BE14" s="5" t="inlineStr">
-        <is>
-          <t>Law 103; LAW 221</t>
+      <c r="AX14" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AY14" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AZ14" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BA14" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BB14" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BC14" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BD14" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BE14" s="4" t="inlineStr">
+        <is>
+          <t> </t>
         </is>
       </c>
       <c r="BF14" s="4" t="inlineStr">
@@ -4778,7 +4778,7 @@
     <row r="15" ht="20" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PALESTROQUE, EARL MATTHEW ZALDARRIAGA</t>
+          <t>JUAN, VERCIL ACUSAR</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -4831,64 +4831,64 @@
           <t> </t>
         </is>
       </c>
-      <c r="L15" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="M15" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="N15" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="O15" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="P15" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="Q15" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="R15" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="S15" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="T15" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="U15" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="V15" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="W15" s="4" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>Physics 142; NIP R109</t>
+        </is>
+      </c>
+      <c r="M15" s="5" t="inlineStr">
+        <is>
+          <t>Physics 142; NIP R109</t>
+        </is>
+      </c>
+      <c r="N15" s="5" t="inlineStr">
+        <is>
+          <t>Physics 142; NIP R109</t>
+        </is>
+      </c>
+      <c r="O15" s="5" t="inlineStr">
+        <is>
+          <t>Physics 142; NIP R109</t>
+        </is>
+      </c>
+      <c r="P15" s="5" t="inlineStr">
+        <is>
+          <t>Physics 142; NIP R109</t>
+        </is>
+      </c>
+      <c r="Q15" s="5" t="inlineStr">
+        <is>
+          <t>Physics 142; NIP R109</t>
+        </is>
+      </c>
+      <c r="R15" s="5" t="inlineStr">
+        <is>
+          <t>Physics 170; NIP R201</t>
+        </is>
+      </c>
+      <c r="S15" s="5" t="inlineStr">
+        <is>
+          <t>Physics 170; NIP R201</t>
+        </is>
+      </c>
+      <c r="T15" s="5" t="inlineStr">
+        <is>
+          <t>Physics 170; NIP R201</t>
+        </is>
+      </c>
+      <c r="U15" s="5" t="inlineStr">
+        <is>
+          <t>Physics 170; NIP R201</t>
+        </is>
+      </c>
+      <c r="V15" s="5" t="inlineStr">
+        <is>
+          <t>Physics 170; NIP R201</t>
+        </is>
+      </c>
+      <c r="W15" s="5" t="inlineStr">
+        <is>
+          <t>Physics 170; NIP R201</t>
         </is>
       </c>
       <c r="X15" s="4" t="inlineStr">
@@ -5021,34 +5021,34 @@
           <t> </t>
         </is>
       </c>
-      <c r="AX15" s="5" t="inlineStr">
-        <is>
-          <t>Law 113; LAW 307-309</t>
-        </is>
-      </c>
-      <c r="AY15" s="5" t="inlineStr">
-        <is>
-          <t>Law 113; LAW 307-309</t>
-        </is>
-      </c>
-      <c r="AZ15" s="5" t="inlineStr">
-        <is>
-          <t>Law 113; LAW 307-309</t>
-        </is>
-      </c>
-      <c r="BA15" s="5" t="inlineStr">
-        <is>
-          <t>Law 113; LAW 307-309</t>
-        </is>
-      </c>
-      <c r="BB15" s="5" t="inlineStr">
-        <is>
-          <t>Law 113; LAW 307-309</t>
-        </is>
-      </c>
-      <c r="BC15" s="5" t="inlineStr">
-        <is>
-          <t>Law 113; LAW 307-309</t>
+      <c r="AX15" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AY15" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AZ15" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BA15" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BB15" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BC15" s="4" t="inlineStr">
+        <is>
+          <t> </t>
         </is>
       </c>
       <c r="BD15" s="4" t="inlineStr">
@@ -5071,24 +5071,24 @@
           <t> </t>
         </is>
       </c>
-      <c r="BH15" s="5" t="inlineStr">
-        <is>
-          <t>Law 105; LAW 307-309</t>
-        </is>
-      </c>
-      <c r="BI15" s="5" t="inlineStr">
-        <is>
-          <t>Law 105; LAW 307-309</t>
-        </is>
-      </c>
-      <c r="BJ15" s="5" t="inlineStr">
-        <is>
-          <t>Law 105; LAW 307-309</t>
-        </is>
-      </c>
-      <c r="BK15" s="5" t="inlineStr">
-        <is>
-          <t>Law 105; LAW 307-309</t>
+      <c r="BH15" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BI15" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BJ15" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BK15" s="4" t="inlineStr">
+        <is>
+          <t> </t>
         </is>
       </c>
       <c r="BL15" s="4" t="inlineStr">
@@ -5105,7 +5105,7 @@
     <row r="16" ht="20" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PANTOJA, JANWIN MYL ROMERO</t>
+          <t>MARASIGAN, MIKE ANTHONY JOSON</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -5168,54 +5168,54 @@
           <t> </t>
         </is>
       </c>
-      <c r="N16" s="5" t="inlineStr">
-        <is>
-          <t>Math 23; TBA</t>
-        </is>
-      </c>
-      <c r="O16" s="5" t="inlineStr">
-        <is>
-          <t>Math 23; TBA</t>
-        </is>
-      </c>
-      <c r="P16" s="5" t="inlineStr">
-        <is>
-          <t>Math 23; TBA</t>
-        </is>
-      </c>
-      <c r="Q16" s="5" t="inlineStr">
-        <is>
-          <t>Math 23; TBA</t>
-        </is>
-      </c>
-      <c r="R16" s="5" t="inlineStr">
-        <is>
-          <t>KAS 1; PH 116-118</t>
-        </is>
-      </c>
-      <c r="S16" s="5" t="inlineStr">
-        <is>
-          <t>KAS 1; PH 116-118</t>
-        </is>
-      </c>
-      <c r="T16" s="5" t="inlineStr">
-        <is>
-          <t>KAS 1; PH 116-118</t>
-        </is>
-      </c>
-      <c r="U16" s="5" t="inlineStr">
-        <is>
-          <t>KAS 1; PH 116-118</t>
-        </is>
-      </c>
-      <c r="V16" s="5" t="inlineStr">
-        <is>
-          <t>KAS 1; PH 116-118</t>
-        </is>
-      </c>
-      <c r="W16" s="5" t="inlineStr">
-        <is>
-          <t>KAS 1; PH 116-118</t>
+      <c r="N16" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="O16" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="P16" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="Q16" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="R16" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="S16" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="T16" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="U16" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="V16" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="W16" s="4" t="inlineStr">
+        <is>
+          <t> </t>
         </is>
       </c>
       <c r="X16" s="4" t="inlineStr">
@@ -5248,34 +5248,34 @@
           <t> </t>
         </is>
       </c>
-      <c r="AD16" s="5" t="inlineStr">
-        <is>
-          <t>EEE 133; EEEI 421</t>
-        </is>
-      </c>
-      <c r="AE16" s="5" t="inlineStr">
-        <is>
-          <t>EEE 133; EEEI 421</t>
-        </is>
-      </c>
-      <c r="AF16" s="5" t="inlineStr">
-        <is>
-          <t>EEE 133; EEEI 421</t>
-        </is>
-      </c>
-      <c r="AG16" s="5" t="inlineStr">
-        <is>
-          <t>EEE 133; EEEI 421</t>
-        </is>
-      </c>
-      <c r="AH16" s="5" t="inlineStr">
-        <is>
-          <t>EEE 133; EEEI 421</t>
-        </is>
-      </c>
-      <c r="AI16" s="5" t="inlineStr">
-        <is>
-          <t>EEE 133; EEEI 421</t>
+      <c r="AD16" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AE16" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AF16" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AG16" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AH16" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AI16" s="4" t="inlineStr">
+        <is>
+          <t> </t>
         </is>
       </c>
       <c r="AJ16" s="4" t="inlineStr">
@@ -5348,44 +5348,44 @@
           <t> </t>
         </is>
       </c>
-      <c r="AX16" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AY16" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AZ16" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="BA16" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="BB16" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="BC16" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="BD16" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="BE16" s="4" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="AX16" s="5" t="inlineStr">
+        <is>
+          <t>Law 103; LAW 221</t>
+        </is>
+      </c>
+      <c r="AY16" s="5" t="inlineStr">
+        <is>
+          <t>Law 103; LAW 221</t>
+        </is>
+      </c>
+      <c r="AZ16" s="5" t="inlineStr">
+        <is>
+          <t>Law 103; LAW 221</t>
+        </is>
+      </c>
+      <c r="BA16" s="5" t="inlineStr">
+        <is>
+          <t>Law 103; LAW 221</t>
+        </is>
+      </c>
+      <c r="BB16" s="5" t="inlineStr">
+        <is>
+          <t>Law 103; LAW 221</t>
+        </is>
+      </c>
+      <c r="BC16" s="5" t="inlineStr">
+        <is>
+          <t>Law 103; LAW 221</t>
+        </is>
+      </c>
+      <c r="BD16" s="5" t="inlineStr">
+        <is>
+          <t>Law 103; LAW 221</t>
+        </is>
+      </c>
+      <c r="BE16" s="5" t="inlineStr">
+        <is>
+          <t>Law 103; LAW 221</t>
         </is>
       </c>
       <c r="BF16" s="4" t="inlineStr">
@@ -5432,325 +5432,1633 @@
     <row r="17" ht="20" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
+          <t>PALESTROQUE, EARL MATTHEW ZALDARRIAGA</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="O17" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="P17" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="Q17" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="R17" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="S17" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="T17" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="U17" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="V17" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="W17" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="X17" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="Y17" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="Z17" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AA17" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AB17" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AC17" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AD17" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AE17" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AF17" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AG17" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AH17" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AI17" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AJ17" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AK17" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AL17" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AM17" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AN17" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AO17" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AP17" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AQ17" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AR17" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AS17" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AT17" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AU17" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AV17" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AW17" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AX17" s="5" t="inlineStr">
+        <is>
+          <t>Law 113; LAW 307-309</t>
+        </is>
+      </c>
+      <c r="AY17" s="5" t="inlineStr">
+        <is>
+          <t>Law 113; LAW 307-309</t>
+        </is>
+      </c>
+      <c r="AZ17" s="5" t="inlineStr">
+        <is>
+          <t>Law 113; LAW 307-309</t>
+        </is>
+      </c>
+      <c r="BA17" s="5" t="inlineStr">
+        <is>
+          <t>Law 113; LAW 307-309</t>
+        </is>
+      </c>
+      <c r="BB17" s="5" t="inlineStr">
+        <is>
+          <t>Law 113; LAW 307-309</t>
+        </is>
+      </c>
+      <c r="BC17" s="5" t="inlineStr">
+        <is>
+          <t>Law 113; LAW 307-309</t>
+        </is>
+      </c>
+      <c r="BD17" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BE17" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BF17" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BG17" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BH17" s="5" t="inlineStr">
+        <is>
+          <t>Law 105; LAW 307-309</t>
+        </is>
+      </c>
+      <c r="BI17" s="5" t="inlineStr">
+        <is>
+          <t>Law 105; LAW 307-309</t>
+        </is>
+      </c>
+      <c r="BJ17" s="5" t="inlineStr">
+        <is>
+          <t>Law 105; LAW 307-309</t>
+        </is>
+      </c>
+      <c r="BK17" s="5" t="inlineStr">
+        <is>
+          <t>Law 105; LAW 307-309</t>
+        </is>
+      </c>
+      <c r="BL17" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BM17" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>PANTOJA, JANWIN MYL ROMERO</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="M18" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="N18" s="5" t="inlineStr">
+        <is>
+          <t>Math 23; TBA</t>
+        </is>
+      </c>
+      <c r="O18" s="5" t="inlineStr">
+        <is>
+          <t>Math 23; TBA</t>
+        </is>
+      </c>
+      <c r="P18" s="5" t="inlineStr">
+        <is>
+          <t>Math 23; TBA</t>
+        </is>
+      </c>
+      <c r="Q18" s="5" t="inlineStr">
+        <is>
+          <t>Math 23; TBA</t>
+        </is>
+      </c>
+      <c r="R18" s="5" t="inlineStr">
+        <is>
+          <t>KAS 1; PH 116-118</t>
+        </is>
+      </c>
+      <c r="S18" s="5" t="inlineStr">
+        <is>
+          <t>KAS 1; PH 116-118</t>
+        </is>
+      </c>
+      <c r="T18" s="5" t="inlineStr">
+        <is>
+          <t>KAS 1; PH 116-118</t>
+        </is>
+      </c>
+      <c r="U18" s="5" t="inlineStr">
+        <is>
+          <t>KAS 1; PH 116-118</t>
+        </is>
+      </c>
+      <c r="V18" s="5" t="inlineStr">
+        <is>
+          <t>KAS 1; PH 116-118</t>
+        </is>
+      </c>
+      <c r="W18" s="5" t="inlineStr">
+        <is>
+          <t>KAS 1; PH 116-118</t>
+        </is>
+      </c>
+      <c r="X18" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="Y18" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="Z18" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AA18" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AB18" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AC18" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AD18" s="5" t="inlineStr">
+        <is>
+          <t>EEE 133; EEEI 421</t>
+        </is>
+      </c>
+      <c r="AE18" s="5" t="inlineStr">
+        <is>
+          <t>EEE 133; EEEI 421</t>
+        </is>
+      </c>
+      <c r="AF18" s="5" t="inlineStr">
+        <is>
+          <t>EEE 133; EEEI 421</t>
+        </is>
+      </c>
+      <c r="AG18" s="5" t="inlineStr">
+        <is>
+          <t>EEE 133; EEEI 421</t>
+        </is>
+      </c>
+      <c r="AH18" s="5" t="inlineStr">
+        <is>
+          <t>EEE 133; EEEI 421</t>
+        </is>
+      </c>
+      <c r="AI18" s="5" t="inlineStr">
+        <is>
+          <t>EEE 133; EEEI 421</t>
+        </is>
+      </c>
+      <c r="AJ18" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AK18" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AL18" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AM18" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AN18" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AO18" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AP18" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AQ18" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AR18" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AS18" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AT18" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AU18" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AV18" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AW18" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AX18" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AY18" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AZ18" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BA18" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BB18" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BC18" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BD18" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BE18" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BF18" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BG18" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BH18" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BI18" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BJ18" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BK18" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BL18" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BM18" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>PASADILLA, JONAS AVRIL</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>Math 21; MB 306</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>Math 21; MB 306</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>Math 21; MB 306</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>Math 21; MB 306</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>Eng 13; CAL 310</t>
+        </is>
+      </c>
+      <c r="M19" s="5" t="inlineStr">
+        <is>
+          <t>Eng 13; CAL 310</t>
+        </is>
+      </c>
+      <c r="N19" s="5" t="inlineStr">
+        <is>
+          <t>Eng 13; CAL 310</t>
+        </is>
+      </c>
+      <c r="O19" s="5" t="inlineStr">
+        <is>
+          <t>Eng 13; CAL 310</t>
+        </is>
+      </c>
+      <c r="P19" s="5" t="inlineStr">
+        <is>
+          <t>Eng 13; CAL 310</t>
+        </is>
+      </c>
+      <c r="Q19" s="5" t="inlineStr">
+        <is>
+          <t>Eng 13; CAL 310</t>
+        </is>
+      </c>
+      <c r="R19" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="S19" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="T19" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="U19" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="V19" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="W19" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="X19" s="5" t="inlineStr">
+        <is>
+          <t>ChemE 101; MH 321</t>
+        </is>
+      </c>
+      <c r="Y19" s="5" t="inlineStr">
+        <is>
+          <t>ChemE 101; MH 321</t>
+        </is>
+      </c>
+      <c r="Z19" s="5" t="inlineStr">
+        <is>
+          <t>ChemE 101; MH 321</t>
+        </is>
+      </c>
+      <c r="AA19" s="5" t="inlineStr">
+        <is>
+          <t>ChemE 101; MH 321</t>
+        </is>
+      </c>
+      <c r="AB19" s="5" t="inlineStr">
+        <is>
+          <t>ChemE 101; MH 321</t>
+        </is>
+      </c>
+      <c r="AC19" s="5" t="inlineStr">
+        <is>
+          <t>ChemE 101; MH 321</t>
+        </is>
+      </c>
+      <c r="AD19" s="5" t="inlineStr">
+        <is>
+          <t>ChemE 101; MH 321</t>
+        </is>
+      </c>
+      <c r="AE19" s="5" t="inlineStr">
+        <is>
+          <t>ChemE 101; MH 321</t>
+        </is>
+      </c>
+      <c r="AF19" s="5" t="inlineStr">
+        <is>
+          <t>ChemE 101; MH 321</t>
+        </is>
+      </c>
+      <c r="AG19" s="5" t="inlineStr">
+        <is>
+          <t>ChemE 101; MH 321</t>
+        </is>
+      </c>
+      <c r="AH19" s="5" t="inlineStr">
+        <is>
+          <t>ChemE 101; MH 321</t>
+        </is>
+      </c>
+      <c r="AI19" s="5" t="inlineStr">
+        <is>
+          <t>ChemE 101; MH 321</t>
+        </is>
+      </c>
+      <c r="AJ19" s="5" t="inlineStr">
+        <is>
+          <t>Physics 71; NIP F203</t>
+        </is>
+      </c>
+      <c r="AK19" s="5" t="inlineStr">
+        <is>
+          <t>Physics 71; NIP F203</t>
+        </is>
+      </c>
+      <c r="AL19" s="5" t="inlineStr">
+        <is>
+          <t>Physics 71; NIP F203</t>
+        </is>
+      </c>
+      <c r="AM19" s="5" t="inlineStr">
+        <is>
+          <t>Physics 71; NIP F203</t>
+        </is>
+      </c>
+      <c r="AN19" s="5" t="inlineStr">
+        <is>
+          <t>Physics 71; NIP F203</t>
+        </is>
+      </c>
+      <c r="AO19" s="5" t="inlineStr">
+        <is>
+          <t>Physics 71; NIP F203</t>
+        </is>
+      </c>
+      <c r="AP19" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AQ19" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AR19" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AS19" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AT19" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AU19" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AV19" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AW19" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AX19" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AY19" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AZ19" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BA19" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BB19" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BC19" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BD19" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BE19" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BF19" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BG19" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BH19" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BI19" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BJ19" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BK19" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BL19" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BM19" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>TAYO, MARCUS JAMES REMO</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>Physics 71; NIP F209</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>Physics 71; NIP F209</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>Physics 71; NIP F209</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>Physics 71; NIP F209</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="N20" s="5" t="inlineStr">
+        <is>
+          <t>PE 2 RF; TBA</t>
+        </is>
+      </c>
+      <c r="O20" s="5" t="inlineStr">
+        <is>
+          <t>PE 2 RF; TBA</t>
+        </is>
+      </c>
+      <c r="P20" s="5" t="inlineStr">
+        <is>
+          <t>PE 2 RF; TBA</t>
+        </is>
+      </c>
+      <c r="Q20" s="5" t="inlineStr">
+        <is>
+          <t>PE 2 RF; TBA</t>
+        </is>
+      </c>
+      <c r="R20" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="S20" s="5" t="inlineStr">
+        <is>
+          <t>Math 21; MB 304</t>
+        </is>
+      </c>
+      <c r="T20" s="5" t="inlineStr">
+        <is>
+          <t>Math 21; MB 304</t>
+        </is>
+      </c>
+      <c r="U20" s="5" t="inlineStr">
+        <is>
+          <t>Math 21; MB 304</t>
+        </is>
+      </c>
+      <c r="V20" s="5" t="inlineStr">
+        <is>
+          <t>Math 21; MB 304</t>
+        </is>
+      </c>
+      <c r="W20" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="X20" s="5" t="inlineStr">
+        <is>
+          <t>EEE 111; EEEI 204</t>
+        </is>
+      </c>
+      <c r="Y20" s="5" t="inlineStr">
+        <is>
+          <t>EEE 111; EEEI 204</t>
+        </is>
+      </c>
+      <c r="Z20" s="5" t="inlineStr">
+        <is>
+          <t>EEE 111; EEEI 204</t>
+        </is>
+      </c>
+      <c r="AA20" s="5" t="inlineStr">
+        <is>
+          <t>EEE 111; EEEI 204</t>
+        </is>
+      </c>
+      <c r="AB20" s="5" t="inlineStr">
+        <is>
+          <t>EEE 111; EEEI 204</t>
+        </is>
+      </c>
+      <c r="AC20" s="5" t="inlineStr">
+        <is>
+          <t>EEE 111; EEEI 204</t>
+        </is>
+      </c>
+      <c r="AD20" s="5" t="inlineStr">
+        <is>
+          <t>EEE 111; EEEI 204</t>
+        </is>
+      </c>
+      <c r="AE20" s="5" t="inlineStr">
+        <is>
+          <t>EEE 111; EEEI 204</t>
+        </is>
+      </c>
+      <c r="AF20" s="5" t="inlineStr">
+        <is>
+          <t>EEE 111; EEEI 204</t>
+        </is>
+      </c>
+      <c r="AG20" s="5" t="inlineStr">
+        <is>
+          <t>EEE 111; EEEI 204</t>
+        </is>
+      </c>
+      <c r="AH20" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AI20" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AJ20" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AK20" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AL20" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AM20" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AN20" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AO20" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AP20" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AQ20" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AR20" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AS20" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AT20" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AU20" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AV20" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AW20" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AX20" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AY20" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AZ20" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BA20" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BB20" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BC20" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BD20" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BE20" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BF20" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BG20" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BH20" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BI20" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BJ20" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BK20" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BL20" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BM20" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>VELDA, ADAM RISH CAIYOD</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="L17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="M17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="N17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="O17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="P17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="Q17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="R17" s="5" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="M21" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="N21" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="O21" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="P21" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="Q21" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="R21" s="5" t="inlineStr">
         <is>
           <t>Physics 108; NIP LP103</t>
         </is>
       </c>
-      <c r="S17" s="5" t="inlineStr">
+      <c r="S21" s="5" t="inlineStr">
         <is>
           <t>Physics 108; NIP LP103</t>
         </is>
       </c>
-      <c r="T17" s="5" t="inlineStr">
+      <c r="T21" s="5" t="inlineStr">
         <is>
           <t>Physics 108; NIP LP103</t>
         </is>
       </c>
-      <c r="U17" s="5" t="inlineStr">
+      <c r="U21" s="5" t="inlineStr">
         <is>
           <t>Physics 108; NIP LP103</t>
         </is>
       </c>
-      <c r="V17" s="5" t="inlineStr">
+      <c r="V21" s="5" t="inlineStr">
         <is>
           <t>Physics 108; NIP LP103</t>
         </is>
       </c>
-      <c r="W17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="X17" s="5" t="inlineStr">
+      <c r="W21" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="X21" s="5" t="inlineStr">
         <is>
           <t>App Physics 155; NIP LP103</t>
         </is>
       </c>
-      <c r="Y17" s="5" t="inlineStr">
+      <c r="Y21" s="5" t="inlineStr">
         <is>
           <t>App Physics 155; NIP LP103</t>
         </is>
       </c>
-      <c r="Z17" s="5" t="inlineStr">
+      <c r="Z21" s="5" t="inlineStr">
         <is>
           <t>App Physics 155; NIP LP103</t>
         </is>
       </c>
-      <c r="AA17" s="5" t="inlineStr">
+      <c r="AA21" s="5" t="inlineStr">
         <is>
           <t>App Physics 155; NIP LP103</t>
         </is>
       </c>
-      <c r="AB17" s="5" t="inlineStr">
+      <c r="AB21" s="5" t="inlineStr">
         <is>
           <t>App Physics 155; NIP LP103</t>
         </is>
       </c>
-      <c r="AC17" s="5" t="inlineStr">
+      <c r="AC21" s="5" t="inlineStr">
         <is>
           <t>App Physics 155; NIP LP103</t>
         </is>
       </c>
-      <c r="AD17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AE17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AF17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AG17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AH17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AI17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AJ17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AK17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AL17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AM17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AN17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AO17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AP17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AQ17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AR17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AS17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AT17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AU17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AV17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AW17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AX17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AY17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AZ17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="BA17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="BB17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="BC17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="BD17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="BE17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="BF17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="BG17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="BH17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="BI17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="BJ17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="BK17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="BL17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="BM17" s="4" t="inlineStr">
+      <c r="AD21" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AE21" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AF21" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AG21" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AH21" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AI21" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AJ21" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AK21" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AL21" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AM21" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AN21" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AO21" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AP21" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AQ21" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AR21" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AS21" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AT21" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AU21" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AV21" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AW21" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AX21" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AY21" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AZ21" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BA21" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BB21" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BC21" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BD21" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BE21" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BF21" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BG21" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BH21" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BI21" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BJ21" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BK21" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BL21" s="4" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="BM21" s="4" t="inlineStr">
         <is>
           <t> </t>
         </is>

--- a/AutoMobChart1.0/truedata/day_schedules/4_Thursday_schedule.xlsx
+++ b/AutoMobChart1.0/truedata/day_schedules/4_Thursday_schedule.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -447,10 +447,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM21"/>
+  <dimension ref="A1:BM19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="39" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
     <col width="4" customWidth="1" min="2" max="2"/>
     <col width="4" customWidth="1" min="3" max="3"/>
     <col width="4" customWidth="1" min="4" max="4"/>
@@ -859,322 +859,322 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="M3" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="P3" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="Q3" s="4" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="R3" s="5" t="inlineStr">
-        <is>
-          <t>EDH 100; ED 108</t>
-        </is>
-      </c>
-      <c r="S3" s="5" t="inlineStr">
-        <is>
-          <t>EDH 100; ED 108</t>
-        </is>
-      </c>
-      <c r="T3" s="5" t="inlineStr">
-        <is>
-          <t>EDH 100; ED 108</t>
-        </is>
-      </c>
-      <c r="U3" s="5" t="inlineStr">
-        <is>
-          <t>EDH 100; ED 108</t>
-        </is>
-      </c>
-      <c r="V3" s="5" t="inlineStr">
-        <is>
-          <t>EDH 100; ED 108</t>
-        </is>
-      </c>
-      <c r="W3" s="5" t="inlineStr">
-        <is>
-          <t>EDH 100; ED 108</t>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="R3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="S3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="T3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="U3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="V3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="W3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="X3" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="Y3" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="Z3" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AA3" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AB3" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AC3" s="4" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AD3" s="5" t="inlineStr">
-        <is>
-          <t>PI 100; PH 1201</t>
-        </is>
-      </c>
-      <c r="AE3" s="5" t="inlineStr">
-        <is>
-          <t>PI 100; PH 1201</t>
-        </is>
-      </c>
-      <c r="AF3" s="5" t="inlineStr">
-        <is>
-          <t>PI 100; PH 1201</t>
-        </is>
-      </c>
-      <c r="AG3" s="5" t="inlineStr">
-        <is>
-          <t>PI 100; PH 1201</t>
-        </is>
-      </c>
-      <c r="AH3" s="5" t="inlineStr">
-        <is>
-          <t>PI 100; PH 1201</t>
-        </is>
-      </c>
-      <c r="AI3" s="5" t="inlineStr">
-        <is>
-          <t>PI 100; PH 1201</t>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AD3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AE3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AF3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AG3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AH3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AI3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AJ3" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AK3" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AL3" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AM3" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AN3" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AO3" s="4" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AP3" s="5" t="inlineStr">
-        <is>
-          <t>PA 152; TBA</t>
-        </is>
-      </c>
-      <c r="AQ3" s="5" t="inlineStr">
-        <is>
-          <t>PA 152; TBA</t>
-        </is>
-      </c>
-      <c r="AR3" s="5" t="inlineStr">
-        <is>
-          <t>PA 152; TBA</t>
-        </is>
-      </c>
-      <c r="AS3" s="5" t="inlineStr">
-        <is>
-          <t>PA 152; TBA</t>
-        </is>
-      </c>
-      <c r="AT3" s="5" t="inlineStr">
-        <is>
-          <t>PA 152; TBA</t>
-        </is>
-      </c>
-      <c r="AU3" s="5" t="inlineStr">
-        <is>
-          <t>PA 152; TBA</t>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AP3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AQ3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AR3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AS3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AT3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AU3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AV3" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AW3" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AX3" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AY3" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AZ3" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BA3" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BB3" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BC3" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BD3" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BE3" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BF3" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BG3" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BH3" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BI3" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BJ3" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BK3" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BL3" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BM3" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1186,322 +1186,322 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="M4" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="O4" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="P4" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="Q4" s="4" t="inlineStr">
-        <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>EEE 148; EEEI 127</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>EEE 148; EEEI 127</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="inlineStr">
+        <is>
+          <t>EEE 148; EEEI 127</t>
+        </is>
+      </c>
+      <c r="O4" s="5" t="inlineStr">
+        <is>
+          <t>EEE 148; EEEI 127</t>
+        </is>
+      </c>
+      <c r="P4" s="5" t="inlineStr">
+        <is>
+          <t>EEE 148; EEEI 127</t>
+        </is>
+      </c>
+      <c r="Q4" s="5" t="inlineStr">
+        <is>
+          <t>EEE 148; EEEI 127</t>
         </is>
       </c>
       <c r="R4" s="5" t="inlineStr">
         <is>
-          <t>Math 23; TBA</t>
+          <t>EEE 148; EEEI 127</t>
         </is>
       </c>
       <c r="S4" s="5" t="inlineStr">
         <is>
-          <t>Math 23; TBA</t>
+          <t>EEE 148; EEEI 127</t>
         </is>
       </c>
       <c r="T4" s="5" t="inlineStr">
         <is>
-          <t>Math 23; TBA</t>
+          <t>EEE 148; EEEI 127</t>
         </is>
       </c>
       <c r="U4" s="5" t="inlineStr">
         <is>
-          <t>Math 23; TBA</t>
-        </is>
-      </c>
-      <c r="V4" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="W4" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="X4" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="Y4" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="Z4" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AA4" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AB4" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AC4" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AD4" s="5" t="inlineStr">
-        <is>
-          <t>MS 1; MSI Sem. Rm.</t>
-        </is>
-      </c>
-      <c r="AE4" s="5" t="inlineStr">
-        <is>
-          <t>MS 1; MSI Sem. Rm.</t>
-        </is>
-      </c>
-      <c r="AF4" s="5" t="inlineStr">
-        <is>
-          <t>MS 1; MSI Sem. Rm.</t>
-        </is>
-      </c>
-      <c r="AG4" s="5" t="inlineStr">
-        <is>
-          <t>MS 1; MSI Sem. Rm.</t>
-        </is>
-      </c>
-      <c r="AH4" s="5" t="inlineStr">
-        <is>
-          <t>MS 1; MSI Sem. Rm.</t>
-        </is>
-      </c>
-      <c r="AI4" s="5" t="inlineStr">
-        <is>
-          <t>MS 1; MSI Sem. Rm.</t>
+          <t>EEE 148; EEEI 127</t>
+        </is>
+      </c>
+      <c r="V4" s="5" t="inlineStr">
+        <is>
+          <t>EEE 148; EEEI 127</t>
+        </is>
+      </c>
+      <c r="W4" s="5" t="inlineStr">
+        <is>
+          <t>EEE 148; EEEI 127</t>
+        </is>
+      </c>
+      <c r="X4" s="5" t="inlineStr">
+        <is>
+          <t>ES 101; ICE 405</t>
+        </is>
+      </c>
+      <c r="Y4" s="5" t="inlineStr">
+        <is>
+          <t>ES 101; ICE 405</t>
+        </is>
+      </c>
+      <c r="Z4" s="5" t="inlineStr">
+        <is>
+          <t>ES 101; ICE 405</t>
+        </is>
+      </c>
+      <c r="AA4" s="5" t="inlineStr">
+        <is>
+          <t>ES 101; ICE 405</t>
+        </is>
+      </c>
+      <c r="AB4" s="5" t="inlineStr">
+        <is>
+          <t>ES 101; ICE 405</t>
+        </is>
+      </c>
+      <c r="AC4" s="5" t="inlineStr">
+        <is>
+          <t>ES 101; ICE 405</t>
+        </is>
+      </c>
+      <c r="AD4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AE4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AF4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AG4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AH4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AI4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AJ4" s="5" t="inlineStr">
         <is>
-          <t>EEE 131; EEEI 123</t>
+          <t>EEE 141; EEEI 229</t>
         </is>
       </c>
       <c r="AK4" s="5" t="inlineStr">
         <is>
-          <t>EEE 131; EEEI 123</t>
+          <t>EEE 141; EEEI 229</t>
         </is>
       </c>
       <c r="AL4" s="5" t="inlineStr">
         <is>
-          <t>EEE 131; EEEI 123</t>
+          <t>EEE 141; EEEI 229</t>
         </is>
       </c>
       <c r="AM4" s="5" t="inlineStr">
         <is>
-          <t>EEE 131; EEEI 123</t>
+          <t>EEE 141; EEEI 229</t>
         </is>
       </c>
       <c r="AN4" s="5" t="inlineStr">
         <is>
-          <t>EEE 131; EEEI 123</t>
+          <t>EEE 141; EEEI 229</t>
         </is>
       </c>
       <c r="AO4" s="5" t="inlineStr">
         <is>
-          <t>EEE 131; EEEI 123</t>
+          <t>EEE 141; EEEI 229</t>
         </is>
       </c>
       <c r="AP4" s="5" t="inlineStr">
         <is>
-          <t>EEE 133; EEEI 420</t>
+          <t>EEE 147; EEEI VLC</t>
         </is>
       </c>
       <c r="AQ4" s="5" t="inlineStr">
         <is>
-          <t>EEE 133; EEEI 420</t>
+          <t>EEE 147; EEEI VLC</t>
         </is>
       </c>
       <c r="AR4" s="5" t="inlineStr">
         <is>
-          <t>EEE 133; EEEI 420</t>
+          <t>EEE 147; EEEI VLC</t>
         </is>
       </c>
       <c r="AS4" s="5" t="inlineStr">
         <is>
-          <t>EEE 133; EEEI 420</t>
+          <t>EEE 147; EEEI VLC</t>
         </is>
       </c>
       <c r="AT4" s="5" t="inlineStr">
         <is>
-          <t>EEE 133; EEEI 420</t>
+          <t>EEE 147; EEEI VLC</t>
         </is>
       </c>
       <c r="AU4" s="5" t="inlineStr">
         <is>
-          <t>EEE 133; EEEI 420</t>
+          <t>EEE 147; EEEI VLC</t>
         </is>
       </c>
       <c r="AV4" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AW4" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AX4" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AY4" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AZ4" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BA4" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BB4" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BC4" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BD4" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BE4" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BF4" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BG4" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BH4" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BI4" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BJ4" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BK4" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BL4" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BM4" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1513,1777 +1513,1777 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="M5" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="O5" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="P5" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="Q5" s="4" t="inlineStr">
-        <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>EEE 143; EEEI 123</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>EEE 143; EEEI 123</t>
+        </is>
+      </c>
+      <c r="N5" s="5" t="inlineStr">
+        <is>
+          <t>EEE 143; EEEI 123</t>
+        </is>
+      </c>
+      <c r="O5" s="5" t="inlineStr">
+        <is>
+          <t>EEE 143; EEEI 123</t>
+        </is>
+      </c>
+      <c r="P5" s="5" t="inlineStr">
+        <is>
+          <t>EEE 143; EEEI 123</t>
+        </is>
+      </c>
+      <c r="Q5" s="5" t="inlineStr">
+        <is>
+          <t>EEE 143; EEEI 123</t>
         </is>
       </c>
       <c r="R5" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="S5" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="T5" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="U5" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="V5" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="W5" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="X5" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="Y5" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="Z5" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AA5" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AB5" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AC5" s="4" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AD5" s="5" t="inlineStr">
-        <is>
-          <t>EEE 133; EEEI 422</t>
-        </is>
-      </c>
-      <c r="AE5" s="5" t="inlineStr">
-        <is>
-          <t>EEE 133; EEEI 422</t>
-        </is>
-      </c>
-      <c r="AF5" s="5" t="inlineStr">
-        <is>
-          <t>EEE 133; EEEI 422</t>
-        </is>
-      </c>
-      <c r="AG5" s="5" t="inlineStr">
-        <is>
-          <t>EEE 133; EEEI 422</t>
-        </is>
-      </c>
-      <c r="AH5" s="5" t="inlineStr">
-        <is>
-          <t>EEE 133; EEEI 422</t>
-        </is>
-      </c>
-      <c r="AI5" s="5" t="inlineStr">
-        <is>
-          <t>EEE 133; EEEI 422</t>
-        </is>
-      </c>
-      <c r="AJ5" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AK5" s="4" t="inlineStr">
-        <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AD5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AE5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AF5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AG5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AH5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AI5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AJ5" s="5" t="inlineStr">
+        <is>
+          <t>EEE 147; EEEI VLC</t>
+        </is>
+      </c>
+      <c r="AK5" s="5" t="inlineStr">
+        <is>
+          <t>EEE 147; EEEI VLC</t>
         </is>
       </c>
       <c r="AL5" s="5" t="inlineStr">
         <is>
-          <t>Math 23; TBA</t>
+          <t>EEE 147; EEEI VLC</t>
         </is>
       </c>
       <c r="AM5" s="5" t="inlineStr">
         <is>
-          <t>Math 23; TBA</t>
+          <t>EEE 147; EEEI VLC</t>
         </is>
       </c>
       <c r="AN5" s="5" t="inlineStr">
         <is>
-          <t>Math 23; TBA</t>
+          <t>EEE 147; EEEI VLC</t>
         </is>
       </c>
       <c r="AO5" s="5" t="inlineStr">
         <is>
-          <t>Math 23; TBA</t>
+          <t>EEE 147; EEEI VLC</t>
         </is>
       </c>
       <c r="AP5" s="5" t="inlineStr">
         <is>
-          <t>EEE 131; EEEI 229</t>
+          <t>ES 101; ICE 405</t>
         </is>
       </c>
       <c r="AQ5" s="5" t="inlineStr">
         <is>
-          <t>EEE 131; EEEI 229</t>
+          <t>ES 101; ICE 405</t>
         </is>
       </c>
       <c r="AR5" s="5" t="inlineStr">
         <is>
-          <t>EEE 131; EEEI 229</t>
+          <t>ES 101; ICE 405</t>
         </is>
       </c>
       <c r="AS5" s="5" t="inlineStr">
         <is>
-          <t>EEE 131; EEEI 229</t>
+          <t>ES 101; ICE 405</t>
         </is>
       </c>
       <c r="AT5" s="5" t="inlineStr">
         <is>
-          <t>EEE 131; EEEI 229</t>
+          <t>ES 101; ICE 405</t>
         </is>
       </c>
       <c r="AU5" s="5" t="inlineStr">
         <is>
-          <t>EEE 131; EEEI 229</t>
+          <t>ES 101; ICE 405</t>
         </is>
       </c>
       <c r="AV5" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AW5" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AX5" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AY5" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AZ5" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BA5" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BB5" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BC5" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BD5" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BE5" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BF5" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BG5" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BH5" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BI5" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BJ5" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BK5" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BL5" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BM5" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CHIW, TSEN YUN CHUN TRES REYES</t>
+          <t>CAYABYAB, CARL JOSE GARCIA</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="P6" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="Q6" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="R6" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="S6" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="T6" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="U6" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="V6" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="W6" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="X6" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="Y6" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="Z6" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AA6" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AB6" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AC6" s="4" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AD6" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AE6" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AF6" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AG6" s="4" t="inlineStr">
-        <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AD6" s="5" t="inlineStr">
+        <is>
+          <t>IE 33; IE-ME 109</t>
+        </is>
+      </c>
+      <c r="AE6" s="5" t="inlineStr">
+        <is>
+          <t>IE 33; IE-ME 109</t>
+        </is>
+      </c>
+      <c r="AF6" s="5" t="inlineStr">
+        <is>
+          <t>IE 33; IE-ME 109</t>
+        </is>
+      </c>
+      <c r="AG6" s="5" t="inlineStr">
+        <is>
+          <t>IE 33; IE-ME 109</t>
         </is>
       </c>
       <c r="AH6" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AI6" s="4" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AJ6" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AK6" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AL6" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AM6" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AN6" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AO6" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AP6" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AQ6" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AR6" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AS6" s="4" t="inlineStr">
-        <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AJ6" s="5" t="inlineStr">
+        <is>
+          <t>IE 32; IE ME Cog Ergo Lab</t>
+        </is>
+      </c>
+      <c r="AK6" s="5" t="inlineStr">
+        <is>
+          <t>IE 32; IE ME Cog Ergo Lab</t>
+        </is>
+      </c>
+      <c r="AL6" s="5" t="inlineStr">
+        <is>
+          <t>IE 32; IE ME Cog Ergo Lab</t>
+        </is>
+      </c>
+      <c r="AM6" s="5" t="inlineStr">
+        <is>
+          <t>IE 32; IE ME Cog Ergo Lab</t>
+        </is>
+      </c>
+      <c r="AN6" s="5" t="inlineStr">
+        <is>
+          <t>IE 32; IE ME Cog Ergo Lab</t>
+        </is>
+      </c>
+      <c r="AO6" s="5" t="inlineStr">
+        <is>
+          <t>IE 32; IE ME Cog Ergo Lab</t>
+        </is>
+      </c>
+      <c r="AP6" s="5" t="inlineStr">
+        <is>
+          <t>IE 32; IE ME Cog Ergo Lab</t>
+        </is>
+      </c>
+      <c r="AQ6" s="5" t="inlineStr">
+        <is>
+          <t>IE 32; IE ME Cog Ergo Lab</t>
+        </is>
+      </c>
+      <c r="AR6" s="5" t="inlineStr">
+        <is>
+          <t>IE 32; IE ME Cog Ergo Lab</t>
+        </is>
+      </c>
+      <c r="AS6" s="5" t="inlineStr">
+        <is>
+          <t>IE 32; IE ME Cog Ergo Lab</t>
         </is>
       </c>
       <c r="AT6" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AU6" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AV6" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AW6" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AX6" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AY6" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AZ6" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BA6" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BB6" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BC6" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BD6" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BE6" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BF6" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BG6" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BH6" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BI6" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BJ6" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BK6" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BL6" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BM6" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CONIENDO, ROLAND CLINT JANDOG</t>
+          <t>CHIW, TSEN YUN CHUN TRES REYES</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="L7" s="5" t="inlineStr">
-        <is>
-          <t>EEE 133; EEEI 421</t>
-        </is>
-      </c>
-      <c r="M7" s="5" t="inlineStr">
-        <is>
-          <t>EEE 133; EEEI 421</t>
-        </is>
-      </c>
-      <c r="N7" s="5" t="inlineStr">
-        <is>
-          <t>EEE 133; EEEI 421</t>
-        </is>
-      </c>
-      <c r="O7" s="5" t="inlineStr">
-        <is>
-          <t>EEE 133; EEEI 421</t>
-        </is>
-      </c>
-      <c r="P7" s="5" t="inlineStr">
-        <is>
-          <t>EEE 133; EEEI 421</t>
-        </is>
-      </c>
-      <c r="Q7" s="5" t="inlineStr">
-        <is>
-          <t>EEE 133; EEEI 421</t>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="O7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="P7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="Q7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="R7" s="5" t="inlineStr">
         <is>
-          <t>Geol 1; NIGS 127</t>
+          <t>BA 193; BA 110</t>
         </is>
       </c>
       <c r="S7" s="5" t="inlineStr">
         <is>
-          <t>Geol 1; NIGS 127</t>
+          <t>BA 193; BA 110</t>
         </is>
       </c>
       <c r="T7" s="5" t="inlineStr">
         <is>
-          <t>Geol 1; NIGS 127</t>
+          <t>BA 193; BA 110</t>
         </is>
       </c>
       <c r="U7" s="5" t="inlineStr">
         <is>
-          <t>Geol 1; NIGS 127</t>
+          <t>BA 193; BA 110</t>
         </is>
       </c>
       <c r="V7" s="5" t="inlineStr">
         <is>
-          <t>Geol 1; NIGS 127</t>
+          <t>BA 193; BA 110</t>
         </is>
       </c>
       <c r="W7" s="5" t="inlineStr">
         <is>
-          <t>Geol 1; NIGS 127</t>
+          <t>BA 193; BA 110</t>
         </is>
       </c>
       <c r="X7" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="Y7" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="Z7" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AA7" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AB7" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AC7" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AD7" s="5" t="inlineStr">
         <is>
-          <t>Math 23; TBA</t>
+          <t>BA 194; BA 307</t>
         </is>
       </c>
       <c r="AE7" s="5" t="inlineStr">
         <is>
-          <t>Math 23; TBA</t>
+          <t>BA 194; BA 307</t>
         </is>
       </c>
       <c r="AF7" s="5" t="inlineStr">
         <is>
-          <t>Math 23; TBA</t>
+          <t>BA 194; BA 307</t>
         </is>
       </c>
       <c r="AG7" s="5" t="inlineStr">
         <is>
-          <t>Math 23; TBA</t>
-        </is>
-      </c>
-      <c r="AH7" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AI7" s="4" t="inlineStr">
-        <is>
-          <t> </t>
+          <t>BA 194; BA 307</t>
+        </is>
+      </c>
+      <c r="AH7" s="5" t="inlineStr">
+        <is>
+          <t>BA 194; BA 307</t>
+        </is>
+      </c>
+      <c r="AI7" s="5" t="inlineStr">
+        <is>
+          <t>BA 194; BA 307</t>
         </is>
       </c>
       <c r="AJ7" s="5" t="inlineStr">
         <is>
-          <t>Math 40; MBAN 301</t>
+          <t>BA 190; BA 309</t>
         </is>
       </c>
       <c r="AK7" s="5" t="inlineStr">
         <is>
-          <t>Math 40; MBAN 301</t>
+          <t>BA 190; BA 309</t>
         </is>
       </c>
       <c r="AL7" s="5" t="inlineStr">
         <is>
-          <t>Math 40; MBAN 301</t>
+          <t>BA 190; BA 309</t>
         </is>
       </c>
       <c r="AM7" s="5" t="inlineStr">
         <is>
-          <t>Math 40; MBAN 301</t>
+          <t>BA 190; BA 309</t>
         </is>
       </c>
       <c r="AN7" s="5" t="inlineStr">
         <is>
-          <t>Math 40; MBAN 301</t>
+          <t>BA 190; BA 309</t>
         </is>
       </c>
       <c r="AO7" s="5" t="inlineStr">
         <is>
-          <t>Math 40; MBAN 301</t>
+          <t>BA 190; BA 309</t>
         </is>
       </c>
       <c r="AP7" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AQ7" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR7" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AS7" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AT7" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AU7" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AV7" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AW7" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AX7" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AY7" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AZ7" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BA7" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BB7" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BC7" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BD7" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BE7" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BF7" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BG7" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BH7" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BI7" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BJ7" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BK7" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BL7" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BM7" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DELA CRUZ, EZECKIEL JOSE SARENAS</t>
+          <t>CHIW, TSEN YUN CHUN TRES REYES</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>Math 21; MB 304</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>Math 21; MB 304</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>Math 21; MB 304</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>Math 21; MB 304</t>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="M8" s="5" t="inlineStr">
-        <is>
-          <t>Physics 71; NIP F209</t>
-        </is>
-      </c>
-      <c r="N8" s="5" t="inlineStr">
-        <is>
-          <t>Physics 71; NIP F209</t>
-        </is>
-      </c>
-      <c r="O8" s="5" t="inlineStr">
-        <is>
-          <t>Physics 71; NIP F209</t>
-        </is>
-      </c>
-      <c r="P8" s="5" t="inlineStr">
-        <is>
-          <t>Physics 71; NIP F209</t>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="O8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="P8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="Q8" s="4" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="R8" s="5" t="inlineStr">
-        <is>
-          <t>Philo 1; PH 222</t>
-        </is>
-      </c>
-      <c r="S8" s="5" t="inlineStr">
-        <is>
-          <t>Philo 1; PH 222</t>
-        </is>
-      </c>
-      <c r="T8" s="5" t="inlineStr">
-        <is>
-          <t>Philo 1; PH 222</t>
-        </is>
-      </c>
-      <c r="U8" s="5" t="inlineStr">
-        <is>
-          <t>Philo 1; PH 222</t>
-        </is>
-      </c>
-      <c r="V8" s="5" t="inlineStr">
-        <is>
-          <t>Philo 1; PH 222</t>
-        </is>
-      </c>
-      <c r="W8" s="5" t="inlineStr">
-        <is>
-          <t>Philo 1; PH 222</t>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="R8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="S8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="T8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="U8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="V8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="W8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="X8" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="Y8" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="Z8" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AA8" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AB8" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AC8" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AD8" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE8" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AF8" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AG8" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AH8" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AI8" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AJ8" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AK8" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AL8" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AM8" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AN8" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AO8" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AP8" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AQ8" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR8" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AS8" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AT8" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AU8" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AV8" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AW8" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AX8" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AY8" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AZ8" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BA8" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BB8" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BC8" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BD8" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BE8" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BF8" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BG8" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BH8" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BI8" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BJ8" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BK8" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BL8" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BM8" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EIMAN, GERTRO FELIX DUMARAOG</t>
+          <t>CONIENDO, ROLAND CLINT JANDOG</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="Q9" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="R9" s="5" t="inlineStr">
         <is>
-          <t>ARTS 1; TBA</t>
+          <t>ES 101; ICE 405</t>
         </is>
       </c>
       <c r="S9" s="5" t="inlineStr">
         <is>
-          <t>ARTS 1; TBA</t>
+          <t>ES 101; ICE 405</t>
         </is>
       </c>
       <c r="T9" s="5" t="inlineStr">
         <is>
-          <t>ARTS 1; TBA</t>
+          <t>ES 101; ICE 405</t>
         </is>
       </c>
       <c r="U9" s="5" t="inlineStr">
         <is>
-          <t>ARTS 1; TBA</t>
+          <t>ES 101; ICE 405</t>
         </is>
       </c>
       <c r="V9" s="5" t="inlineStr">
         <is>
-          <t>ARTS 1; TBA</t>
+          <t>ES 101; ICE 405</t>
         </is>
       </c>
       <c r="W9" s="5" t="inlineStr">
         <is>
-          <t>ARTS 1; TBA</t>
-        </is>
-      </c>
-      <c r="X9" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="Y9" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="Z9" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AA9" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AB9" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AC9" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AD9" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AE9" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AF9" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AG9" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AH9" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AI9" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AJ9" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AK9" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AL9" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AM9" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AN9" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AO9" s="4" t="inlineStr">
-        <is>
-          <t> </t>
+          <t>ES 101; ICE 405</t>
+        </is>
+      </c>
+      <c r="X9" s="5" t="inlineStr">
+        <is>
+          <t>EEE 145; EEEI 422</t>
+        </is>
+      </c>
+      <c r="Y9" s="5" t="inlineStr">
+        <is>
+          <t>EEE 145; EEEI 422</t>
+        </is>
+      </c>
+      <c r="Z9" s="5" t="inlineStr">
+        <is>
+          <t>EEE 145; EEEI 422</t>
+        </is>
+      </c>
+      <c r="AA9" s="5" t="inlineStr">
+        <is>
+          <t>EEE 145; EEEI 422</t>
+        </is>
+      </c>
+      <c r="AB9" s="5" t="inlineStr">
+        <is>
+          <t>EEE 145; EEEI 422</t>
+        </is>
+      </c>
+      <c r="AC9" s="5" t="inlineStr">
+        <is>
+          <t>EEE 145; EEEI 422</t>
+        </is>
+      </c>
+      <c r="AD9" s="5" t="inlineStr">
+        <is>
+          <t>EEE 141; EEEI 229</t>
+        </is>
+      </c>
+      <c r="AE9" s="5" t="inlineStr">
+        <is>
+          <t>EEE 141; EEEI 229</t>
+        </is>
+      </c>
+      <c r="AF9" s="5" t="inlineStr">
+        <is>
+          <t>EEE 141; EEEI 229</t>
+        </is>
+      </c>
+      <c r="AG9" s="5" t="inlineStr">
+        <is>
+          <t>EEE 141; EEEI 229</t>
+        </is>
+      </c>
+      <c r="AH9" s="5" t="inlineStr">
+        <is>
+          <t>EEE 141; EEEI 229</t>
+        </is>
+      </c>
+      <c r="AI9" s="5" t="inlineStr">
+        <is>
+          <t>EEE 141; EEEI 229</t>
+        </is>
+      </c>
+      <c r="AJ9" s="5" t="inlineStr">
+        <is>
+          <t>EEE 147; EEEI VLC</t>
+        </is>
+      </c>
+      <c r="AK9" s="5" t="inlineStr">
+        <is>
+          <t>EEE 147; EEEI VLC</t>
+        </is>
+      </c>
+      <c r="AL9" s="5" t="inlineStr">
+        <is>
+          <t>EEE 147; EEEI VLC</t>
+        </is>
+      </c>
+      <c r="AM9" s="5" t="inlineStr">
+        <is>
+          <t>EEE 147; EEEI VLC</t>
+        </is>
+      </c>
+      <c r="AN9" s="5" t="inlineStr">
+        <is>
+          <t>EEE 147; EEEI VLC</t>
+        </is>
+      </c>
+      <c r="AO9" s="5" t="inlineStr">
+        <is>
+          <t>EEE 147; EEEI VLC</t>
         </is>
       </c>
       <c r="AP9" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AQ9" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR9" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AS9" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AT9" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AU9" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AV9" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AW9" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AX9" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AY9" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AZ9" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BA9" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BB9" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BC9" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BD9" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BE9" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BF9" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BG9" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BH9" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BI9" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BJ9" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BK9" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BL9" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BM9" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EMPERUA, JUSTIN KYLE LAGAYAN</t>
+          <t>CONIENDO, ROLAND CLINT JANDOG</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="J10" s="5" t="inlineStr">
-        <is>
-          <t>GE 161; MH 318-320</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>GE 161; MH 318-320</t>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>GE 161; MH 318-320</t>
+          <t>EEE 133; EEEI 421</t>
         </is>
       </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
-          <t>GE 161; MH 318-320</t>
+          <t>EEE 133; EEEI 421</t>
         </is>
       </c>
       <c r="N10" s="5" t="inlineStr">
         <is>
-          <t>GE 161; MH 318-320</t>
+          <t>EEE 133; EEEI 421</t>
         </is>
       </c>
       <c r="O10" s="5" t="inlineStr">
         <is>
-          <t>GE 161; MH 318-320</t>
+          <t>EEE 133; EEEI 421</t>
         </is>
       </c>
       <c r="P10" s="5" t="inlineStr">
         <is>
-          <t>GE 161; MH 318-320</t>
+          <t>EEE 133; EEEI 421</t>
         </is>
       </c>
       <c r="Q10" s="5" t="inlineStr">
         <is>
-          <t>GE 161; MH 318-320</t>
+          <t>EEE 133; EEEI 421</t>
         </is>
       </c>
       <c r="R10" s="5" t="inlineStr">
         <is>
-          <t>GE 161; MH 318-320</t>
+          <t>Geol 1; NIGS 127</t>
         </is>
       </c>
       <c r="S10" s="5" t="inlineStr">
         <is>
-          <t>GE 161; MH 318-320</t>
+          <t>Geol 1; NIGS 127</t>
         </is>
       </c>
       <c r="T10" s="5" t="inlineStr">
         <is>
-          <t>GE 161; MH 318-320</t>
+          <t>Geol 1; NIGS 127</t>
         </is>
       </c>
       <c r="U10" s="5" t="inlineStr">
         <is>
-          <t>GE 161; MH 318-320</t>
-        </is>
-      </c>
-      <c r="V10" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="W10" s="4" t="inlineStr">
-        <is>
-          <t> </t>
+          <t>Geol 1; NIGS 127</t>
+        </is>
+      </c>
+      <c r="V10" s="5" t="inlineStr">
+        <is>
+          <t>Geol 1; NIGS 127</t>
+        </is>
+      </c>
+      <c r="W10" s="5" t="inlineStr">
+        <is>
+          <t>Geol 1; NIGS 127</t>
         </is>
       </c>
       <c r="X10" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="Y10" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="Z10" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AA10" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AB10" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AC10" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AD10" s="5" t="inlineStr">
@@ -3308,1470 +3308,1470 @@
       </c>
       <c r="AH10" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AI10" s="4" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AJ10" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AK10" s="4" t="inlineStr">
-        <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AJ10" s="5" t="inlineStr">
+        <is>
+          <t>Math 40; MBAN 301</t>
+        </is>
+      </c>
+      <c r="AK10" s="5" t="inlineStr">
+        <is>
+          <t>Math 40; MBAN 301</t>
         </is>
       </c>
       <c r="AL10" s="5" t="inlineStr">
         <is>
-          <t>GE 122; MH 416-418</t>
+          <t>Math 40; MBAN 301</t>
         </is>
       </c>
       <c r="AM10" s="5" t="inlineStr">
         <is>
-          <t>GE 122; MH 416-418</t>
+          <t>Math 40; MBAN 301</t>
         </is>
       </c>
       <c r="AN10" s="5" t="inlineStr">
         <is>
-          <t>GE 122; MH 416-418</t>
+          <t>Math 40; MBAN 301</t>
         </is>
       </c>
       <c r="AO10" s="5" t="inlineStr">
         <is>
-          <t>GE 122; MH 416-418</t>
-        </is>
-      </c>
-      <c r="AP10" s="5" t="inlineStr">
-        <is>
-          <t>GE 122; MH 416-418</t>
-        </is>
-      </c>
-      <c r="AQ10" s="5" t="inlineStr">
-        <is>
-          <t>GE 122; MH 416-418</t>
-        </is>
-      </c>
-      <c r="AR10" s="5" t="inlineStr">
-        <is>
-          <t>GE 122; MH 416-418</t>
-        </is>
-      </c>
-      <c r="AS10" s="5" t="inlineStr">
-        <is>
-          <t>GE 122; MH 416-418</t>
-        </is>
-      </c>
-      <c r="AT10" s="5" t="inlineStr">
-        <is>
-          <t>GE 122; MH 416-418</t>
-        </is>
-      </c>
-      <c r="AU10" s="5" t="inlineStr">
-        <is>
-          <t>GE 122; MH 416-418</t>
-        </is>
-      </c>
-      <c r="AV10" s="5" t="inlineStr">
-        <is>
-          <t>GE 122; MH 416-418</t>
-        </is>
-      </c>
-      <c r="AW10" s="5" t="inlineStr">
-        <is>
-          <t>GE 122; MH 416-418</t>
+          <t>Math 40; MBAN 301</t>
+        </is>
+      </c>
+      <c r="AP10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AQ10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AR10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AS10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AT10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AU10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AV10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AW10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AX10" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AY10" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AZ10" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BA10" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BB10" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BC10" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BD10" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BE10" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BF10" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BG10" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BH10" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BI10" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BJ10" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BK10" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BL10" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BM10" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FERNANDEZ, JAM BASA</t>
+          <t>DELA CRUZ, EZECKIEL JOSE SARENAS</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="L11" s="5" t="inlineStr">
-        <is>
-          <t>Physics 107; NIP F202</t>
-        </is>
-      </c>
-      <c r="M11" s="5" t="inlineStr">
-        <is>
-          <t>Physics 107; NIP F202</t>
-        </is>
-      </c>
-      <c r="N11" s="5" t="inlineStr">
-        <is>
-          <t>Physics 107; NIP F202</t>
-        </is>
-      </c>
-      <c r="O11" s="5" t="inlineStr">
-        <is>
-          <t>Physics 107; NIP F202</t>
-        </is>
-      </c>
-      <c r="P11" s="5" t="inlineStr">
-        <is>
-          <t>Physics 107; NIP F202</t>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="O11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="P11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="Q11" s="4" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="R11" s="5" t="inlineStr">
-        <is>
-          <t>Physics 116; NIP LP101</t>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="R11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="S11" s="5" t="inlineStr">
         <is>
-          <t>Physics 116; NIP LP101</t>
+          <t>Physics 72; NIP F209</t>
         </is>
       </c>
       <c r="T11" s="5" t="inlineStr">
         <is>
-          <t>Physics 116; NIP LP101</t>
+          <t>Physics 72; NIP F209</t>
         </is>
       </c>
       <c r="U11" s="5" t="inlineStr">
         <is>
-          <t>Physics 116; NIP LP101</t>
+          <t>Physics 72; NIP F209</t>
         </is>
       </c>
       <c r="V11" s="5" t="inlineStr">
         <is>
-          <t>Physics 116; NIP LP101</t>
+          <t>Physics 72; NIP F209</t>
         </is>
       </c>
       <c r="W11" s="4" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="X11" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="Y11" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="Z11" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AA11" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AB11" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AC11" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AD11" s="5" t="inlineStr">
-        <is>
-          <t>Math 23; TBA</t>
-        </is>
-      </c>
-      <c r="AE11" s="5" t="inlineStr">
-        <is>
-          <t>Math 23; TBA</t>
-        </is>
-      </c>
-      <c r="AF11" s="5" t="inlineStr">
-        <is>
-          <t>Math 23; TBA</t>
-        </is>
-      </c>
-      <c r="AG11" s="5" t="inlineStr">
-        <is>
-          <t>Math 23; TBA</t>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="X11" s="5" t="inlineStr">
+        <is>
+          <t>Math 22; MB 304</t>
+        </is>
+      </c>
+      <c r="Y11" s="5" t="inlineStr">
+        <is>
+          <t>Math 22; MB 304</t>
+        </is>
+      </c>
+      <c r="Z11" s="5" t="inlineStr">
+        <is>
+          <t>Math 22; MB 304</t>
+        </is>
+      </c>
+      <c r="AA11" s="5" t="inlineStr">
+        <is>
+          <t>Math 22; MB 304</t>
+        </is>
+      </c>
+      <c r="AB11" s="5" t="inlineStr">
+        <is>
+          <t>Math 22; MB 304</t>
+        </is>
+      </c>
+      <c r="AC11" s="5" t="inlineStr">
+        <is>
+          <t>Math 22; MB 304</t>
+        </is>
+      </c>
+      <c r="AD11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AE11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AF11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AG11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AH11" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AI11" s="4" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AJ11" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AK11" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AL11" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AM11" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AN11" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AO11" s="4" t="inlineStr">
-        <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AJ11" s="5" t="inlineStr">
+        <is>
+          <t>EEE 123; EEEI 123</t>
+        </is>
+      </c>
+      <c r="AK11" s="5" t="inlineStr">
+        <is>
+          <t>EEE 123; EEEI 123</t>
+        </is>
+      </c>
+      <c r="AL11" s="5" t="inlineStr">
+        <is>
+          <t>EEE 123; EEEI 123</t>
+        </is>
+      </c>
+      <c r="AM11" s="5" t="inlineStr">
+        <is>
+          <t>EEE 123; EEEI 123</t>
+        </is>
+      </c>
+      <c r="AN11" s="5" t="inlineStr">
+        <is>
+          <t>EEE 123; EEEI 123</t>
+        </is>
+      </c>
+      <c r="AO11" s="5" t="inlineStr">
+        <is>
+          <t>EEE 123; EEEI 123</t>
         </is>
       </c>
       <c r="AP11" s="5" t="inlineStr">
         <is>
-          <t>Math 122; MB 120</t>
+          <t>Speech 30; TBA</t>
         </is>
       </c>
       <c r="AQ11" s="5" t="inlineStr">
         <is>
-          <t>Math 122; MB 120</t>
+          <t>Speech 30; TBA</t>
         </is>
       </c>
       <c r="AR11" s="5" t="inlineStr">
         <is>
-          <t>Math 122; MB 120</t>
+          <t>Speech 30; TBA</t>
         </is>
       </c>
       <c r="AS11" s="5" t="inlineStr">
         <is>
-          <t>Math 122; MB 120</t>
+          <t>Speech 30; TBA</t>
         </is>
       </c>
       <c r="AT11" s="5" t="inlineStr">
         <is>
-          <t>Math 122; MB 120</t>
+          <t>Speech 30; TBA</t>
         </is>
       </c>
       <c r="AU11" s="5" t="inlineStr">
         <is>
-          <t>Math 122; MB 120</t>
+          <t>Speech 30; TBA</t>
         </is>
       </c>
       <c r="AV11" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AW11" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AX11" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AY11" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AZ11" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BA11" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BB11" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BC11" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BD11" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BE11" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BF11" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BG11" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BH11" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BI11" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BJ11" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BK11" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BL11" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BM11" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GAVILAN, SEAN CEDRICK JACOBE</t>
+          <t>EIMAN, GERTRO FELIX DUMARAOG</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="Q12" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="R12" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="T12" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="U12" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="V12" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="W12" s="4" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="X12" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="Y12" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="Z12" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AA12" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AB12" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AC12" s="4" t="inlineStr">
-        <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="X12" s="5" t="inlineStr">
+        <is>
+          <t>Stat 117; SS 301</t>
+        </is>
+      </c>
+      <c r="Y12" s="5" t="inlineStr">
+        <is>
+          <t>Stat 117; SS 301</t>
+        </is>
+      </c>
+      <c r="Z12" s="5" t="inlineStr">
+        <is>
+          <t>Stat 117; SS 301</t>
+        </is>
+      </c>
+      <c r="AA12" s="5" t="inlineStr">
+        <is>
+          <t>Stat 117; SS 301</t>
+        </is>
+      </c>
+      <c r="AB12" s="5" t="inlineStr">
+        <is>
+          <t>Stat 117; SS 301</t>
+        </is>
+      </c>
+      <c r="AC12" s="5" t="inlineStr">
+        <is>
+          <t>Stat 117; SS 301</t>
         </is>
       </c>
       <c r="AD12" s="5" t="inlineStr">
         <is>
-          <t>Archaeo 2; Classroom B</t>
+          <t>Stat 115; SS 432</t>
         </is>
       </c>
       <c r="AE12" s="5" t="inlineStr">
         <is>
-          <t>Archaeo 2; Classroom B</t>
+          <t>Stat 115; SS 432</t>
         </is>
       </c>
       <c r="AF12" s="5" t="inlineStr">
         <is>
-          <t>Archaeo 2; Classroom B</t>
+          <t>Stat 115; SS 432</t>
         </is>
       </c>
       <c r="AG12" s="5" t="inlineStr">
         <is>
-          <t>Archaeo 2; Classroom B</t>
+          <t>Stat 115; SS 432</t>
         </is>
       </c>
       <c r="AH12" s="5" t="inlineStr">
         <is>
-          <t>Archaeo 2; Classroom B</t>
+          <t>Stat 115; SS 432</t>
         </is>
       </c>
       <c r="AI12" s="5" t="inlineStr">
         <is>
-          <t>Archaeo 2; Classroom B</t>
+          <t>Stat 115; SS 432</t>
         </is>
       </c>
       <c r="AJ12" s="4" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AK12" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AL12" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AM12" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AN12" s="4" t="inlineStr">
-        <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AK12" s="5" t="inlineStr">
+        <is>
+          <t>Math 21; TBA</t>
+        </is>
+      </c>
+      <c r="AL12" s="5" t="inlineStr">
+        <is>
+          <t>Math 21; TBA</t>
+        </is>
+      </c>
+      <c r="AM12" s="5" t="inlineStr">
+        <is>
+          <t>Math 21; TBA</t>
+        </is>
+      </c>
+      <c r="AN12" s="5" t="inlineStr">
+        <is>
+          <t>Math 21; TBA</t>
         </is>
       </c>
       <c r="AO12" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AP12" s="4" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AQ12" s="5" t="inlineStr">
-        <is>
-          <t>Math 21; MB 307</t>
-        </is>
-      </c>
-      <c r="AR12" s="5" t="inlineStr">
-        <is>
-          <t>Math 21; MB 307</t>
-        </is>
-      </c>
-      <c r="AS12" s="5" t="inlineStr">
-        <is>
-          <t>Math 21; MB 307</t>
-        </is>
-      </c>
-      <c r="AT12" s="5" t="inlineStr">
-        <is>
-          <t>Math 21; MB 307</t>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AQ12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AR12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AS12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AT12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AU12" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AV12" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AW12" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AX12" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AY12" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AZ12" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BA12" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BB12" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BC12" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BD12" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BE12" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BF12" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BG12" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BH12" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BI12" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BJ12" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BK12" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BL12" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GOCHUICO, AKHILLIS DELA CRUZ</t>
+          <t>EMPERUA, JUSTIN KYLE LAGAYAN</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="L13" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="M13" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="N13" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="O13" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="P13" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="Q13" s="4" t="inlineStr">
-        <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>GE 161; MH 318-320</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>GE 161; MH 318-320</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>GE 161; MH 318-320</t>
+        </is>
+      </c>
+      <c r="M13" s="5" t="inlineStr">
+        <is>
+          <t>GE 161; MH 318-320</t>
+        </is>
+      </c>
+      <c r="N13" s="5" t="inlineStr">
+        <is>
+          <t>GE 161; MH 318-320</t>
+        </is>
+      </c>
+      <c r="O13" s="5" t="inlineStr">
+        <is>
+          <t>GE 161; MH 318-320</t>
+        </is>
+      </c>
+      <c r="P13" s="5" t="inlineStr">
+        <is>
+          <t>GE 161; MH 318-320</t>
+        </is>
+      </c>
+      <c r="Q13" s="5" t="inlineStr">
+        <is>
+          <t>GE 161; MH 318-320</t>
         </is>
       </c>
       <c r="R13" s="5" t="inlineStr">
         <is>
-          <t>Acctg 1; BA 208</t>
+          <t>GE 161; MH 318-320</t>
         </is>
       </c>
       <c r="S13" s="5" t="inlineStr">
         <is>
-          <t>Acctg 1; BA 208</t>
+          <t>GE 161; MH 318-320</t>
         </is>
       </c>
       <c r="T13" s="5" t="inlineStr">
         <is>
-          <t>Acctg 1; BA 208</t>
+          <t>GE 161; MH 318-320</t>
         </is>
       </c>
       <c r="U13" s="5" t="inlineStr">
         <is>
-          <t>Acctg 1; BA 208</t>
-        </is>
-      </c>
-      <c r="V13" s="5" t="inlineStr">
-        <is>
-          <t>Acctg 1; BA 208</t>
-        </is>
-      </c>
-      <c r="W13" s="5" t="inlineStr">
-        <is>
-          <t>Acctg 1; BA 208</t>
-        </is>
-      </c>
-      <c r="X13" s="5" t="inlineStr">
-        <is>
-          <t>IE 27; IE-ME 111</t>
-        </is>
-      </c>
-      <c r="Y13" s="5" t="inlineStr">
-        <is>
-          <t>IE 27; IE-ME 111</t>
-        </is>
-      </c>
-      <c r="Z13" s="5" t="inlineStr">
-        <is>
-          <t>IE 27; IE-ME 111</t>
-        </is>
-      </c>
-      <c r="AA13" s="5" t="inlineStr">
-        <is>
-          <t>IE 27; IE-ME 111</t>
-        </is>
-      </c>
-      <c r="AB13" s="5" t="inlineStr">
-        <is>
-          <t>IE 27; IE-ME 111</t>
-        </is>
-      </c>
-      <c r="AC13" s="5" t="inlineStr">
-        <is>
-          <t>IE 27; IE-ME 111</t>
+          <t>GE 161; MH 318-320</t>
+        </is>
+      </c>
+      <c r="V13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="W13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="X13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="Y13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="Z13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AA13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AB13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AC13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AD13" s="5" t="inlineStr">
         <is>
-          <t>IE 21; MH 417-419</t>
+          <t>Math 23; TBA</t>
         </is>
       </c>
       <c r="AE13" s="5" t="inlineStr">
         <is>
-          <t>IE 21; MH 417-419</t>
+          <t>Math 23; TBA</t>
         </is>
       </c>
       <c r="AF13" s="5" t="inlineStr">
         <is>
-          <t>IE 21; MH 417-419</t>
+          <t>Math 23; TBA</t>
         </is>
       </c>
       <c r="AG13" s="5" t="inlineStr">
         <is>
-          <t>IE 21; MH 417-419</t>
-        </is>
-      </c>
-      <c r="AH13" s="5" t="inlineStr">
-        <is>
-          <t>IE 21; MH 417-419</t>
-        </is>
-      </c>
-      <c r="AI13" s="5" t="inlineStr">
-        <is>
-          <t>IE 21; MH 417-419</t>
-        </is>
-      </c>
-      <c r="AJ13" s="5" t="inlineStr">
-        <is>
-          <t>IE 40; TBA</t>
-        </is>
-      </c>
-      <c r="AK13" s="5" t="inlineStr">
-        <is>
-          <t>IE 40; TBA</t>
+          <t>Math 23; TBA</t>
+        </is>
+      </c>
+      <c r="AH13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AI13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AJ13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AK13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AL13" s="5" t="inlineStr">
         <is>
-          <t>IE 40; TBA</t>
+          <t>GE 122; MH 416-418</t>
         </is>
       </c>
       <c r="AM13" s="5" t="inlineStr">
         <is>
-          <t>IE 40; TBA</t>
+          <t>GE 122; MH 416-418</t>
         </is>
       </c>
       <c r="AN13" s="5" t="inlineStr">
         <is>
-          <t>IE 40; TBA</t>
+          <t>GE 122; MH 416-418</t>
         </is>
       </c>
       <c r="AO13" s="5" t="inlineStr">
         <is>
-          <t>IE 40; TBA</t>
-        </is>
-      </c>
-      <c r="AP13" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AQ13" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AR13" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AS13" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AT13" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AU13" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AV13" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AW13" s="4" t="inlineStr">
-        <is>
-          <t> </t>
+          <t>GE 122; MH 416-418</t>
+        </is>
+      </c>
+      <c r="AP13" s="5" t="inlineStr">
+        <is>
+          <t>GE 122; MH 416-418</t>
+        </is>
+      </c>
+      <c r="AQ13" s="5" t="inlineStr">
+        <is>
+          <t>GE 122; MH 416-418</t>
+        </is>
+      </c>
+      <c r="AR13" s="5" t="inlineStr">
+        <is>
+          <t>GE 122; MH 416-418</t>
+        </is>
+      </c>
+      <c r="AS13" s="5" t="inlineStr">
+        <is>
+          <t>GE 122; MH 416-418</t>
+        </is>
+      </c>
+      <c r="AT13" s="5" t="inlineStr">
+        <is>
+          <t>GE 122; MH 416-418</t>
+        </is>
+      </c>
+      <c r="AU13" s="5" t="inlineStr">
+        <is>
+          <t>GE 122; MH 416-418</t>
+        </is>
+      </c>
+      <c r="AV13" s="5" t="inlineStr">
+        <is>
+          <t>GE 122; MH 416-418</t>
+        </is>
+      </c>
+      <c r="AW13" s="5" t="inlineStr">
+        <is>
+          <t>GE 122; MH 416-418</t>
         </is>
       </c>
       <c r="AX13" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AY13" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AZ13" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BA13" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BB13" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BC13" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BD13" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BE13" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BF13" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BG13" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BH13" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BI13" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BJ13" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BK13" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BL13" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IBAY, DOMINIC JOB MORALES</t>
+          <t>GAVILAN, SEAN CEDRICK JACOBE</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="L14" s="5" t="inlineStr">
-        <is>
-          <t>Physics 142; NIP R109</t>
-        </is>
-      </c>
-      <c r="M14" s="5" t="inlineStr">
-        <is>
-          <t>Physics 142; NIP R109</t>
-        </is>
-      </c>
-      <c r="N14" s="5" t="inlineStr">
-        <is>
-          <t>Physics 142; NIP R109</t>
-        </is>
-      </c>
-      <c r="O14" s="5" t="inlineStr">
-        <is>
-          <t>Physics 142; NIP R109</t>
-        </is>
-      </c>
-      <c r="P14" s="5" t="inlineStr">
-        <is>
-          <t>Physics 142; NIP R109</t>
-        </is>
-      </c>
-      <c r="Q14" s="5" t="inlineStr">
-        <is>
-          <t>Physics 142; NIP R109</t>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="M14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="N14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="O14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="P14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="Q14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="R14" s="5" t="inlineStr">
         <is>
-          <t>Physics 170; NIP F202</t>
+          <t>Geol 1; NIGS 127</t>
         </is>
       </c>
       <c r="S14" s="5" t="inlineStr">
         <is>
-          <t>Physics 170; NIP F202</t>
+          <t>Geol 1; NIGS 127</t>
         </is>
       </c>
       <c r="T14" s="5" t="inlineStr">
         <is>
-          <t>Physics 170; NIP F202</t>
+          <t>Geol 1; NIGS 127</t>
         </is>
       </c>
       <c r="U14" s="5" t="inlineStr">
         <is>
-          <t>Physics 170; NIP F202</t>
+          <t>Geol 1; NIGS 127</t>
         </is>
       </c>
       <c r="V14" s="5" t="inlineStr">
         <is>
-          <t>Physics 170; NIP F202</t>
+          <t>Geol 1; NIGS 127</t>
         </is>
       </c>
       <c r="W14" s="5" t="inlineStr">
         <is>
-          <t>Physics 170; NIP F202</t>
-        </is>
-      </c>
-      <c r="X14" s="5" t="inlineStr">
-        <is>
-          <t>App Physics 167; NIP R109</t>
-        </is>
-      </c>
-      <c r="Y14" s="5" t="inlineStr">
-        <is>
-          <t>App Physics 167; NIP R109</t>
-        </is>
-      </c>
-      <c r="Z14" s="5" t="inlineStr">
-        <is>
-          <t>App Physics 167; NIP R109</t>
-        </is>
-      </c>
-      <c r="AA14" s="5" t="inlineStr">
-        <is>
-          <t>App Physics 167; NIP R109</t>
-        </is>
-      </c>
-      <c r="AB14" s="5" t="inlineStr">
-        <is>
-          <t>App Physics 167; NIP R109</t>
-        </is>
-      </c>
-      <c r="AC14" s="5" t="inlineStr">
-        <is>
-          <t>App Physics 167; NIP R109</t>
+          <t>Geol 1; NIGS 127</t>
+        </is>
+      </c>
+      <c r="X14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="Y14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="Z14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AA14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AB14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AC14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AD14" s="5" t="inlineStr">
         <is>
-          <t>Physics 192; TBA</t>
+          <t>PA 101; TBA</t>
         </is>
       </c>
       <c r="AE14" s="5" t="inlineStr">
         <is>
-          <t>Physics 192; TBA</t>
+          <t>PA 101; TBA</t>
         </is>
       </c>
       <c r="AF14" s="5" t="inlineStr">
         <is>
-          <t>Physics 192; TBA</t>
+          <t>PA 101; TBA</t>
         </is>
       </c>
       <c r="AG14" s="5" t="inlineStr">
         <is>
-          <t>Physics 192; TBA</t>
+          <t>PA 101; TBA</t>
         </is>
       </c>
       <c r="AH14" s="5" t="inlineStr">
         <is>
-          <t>Physics 192; TBA</t>
+          <t>PA 101; TBA</t>
         </is>
       </c>
       <c r="AI14" s="5" t="inlineStr">
         <is>
-          <t>Physics 192; TBA</t>
+          <t>PA 101; TBA</t>
         </is>
       </c>
       <c r="AJ14" s="5" t="inlineStr">
         <is>
-          <t>Physics 192; TBA</t>
+          <t>PA 101; TBA</t>
         </is>
       </c>
       <c r="AK14" s="5" t="inlineStr">
         <is>
-          <t>Physics 192; TBA</t>
+          <t>PA 101; TBA</t>
         </is>
       </c>
       <c r="AL14" s="5" t="inlineStr">
         <is>
-          <t>Physics 192; TBA</t>
+          <t>PA 101; TBA</t>
         </is>
       </c>
       <c r="AM14" s="5" t="inlineStr">
         <is>
-          <t>Physics 192; TBA</t>
+          <t>PA 101; TBA</t>
         </is>
       </c>
       <c r="AN14" s="5" t="inlineStr">
         <is>
-          <t>Physics 192; TBA</t>
+          <t>PA 101; TBA</t>
         </is>
       </c>
       <c r="AO14" s="5" t="inlineStr">
         <is>
-          <t>Physics 192; TBA</t>
+          <t>PA 101; TBA</t>
         </is>
       </c>
       <c r="AP14" s="5" t="inlineStr">
         <is>
-          <t>App Physics 184; NIP R201</t>
+          <t>Math 10; MB 118</t>
         </is>
       </c>
       <c r="AQ14" s="5" t="inlineStr">
         <is>
-          <t>App Physics 184; NIP R201</t>
+          <t>Math 10; MB 118</t>
         </is>
       </c>
       <c r="AR14" s="5" t="inlineStr">
         <is>
-          <t>App Physics 184; NIP R201</t>
+          <t>Math 10; MB 118</t>
         </is>
       </c>
       <c r="AS14" s="5" t="inlineStr">
         <is>
-          <t>App Physics 184; NIP R201</t>
+          <t>Math 10; MB 118</t>
         </is>
       </c>
       <c r="AT14" s="5" t="inlineStr">
         <is>
-          <t>App Physics 184; NIP R201</t>
+          <t>Math 10; MB 118</t>
         </is>
       </c>
       <c r="AU14" s="5" t="inlineStr">
         <is>
-          <t>App Physics 184; NIP R201</t>
+          <t>Math 10; MB 118</t>
         </is>
       </c>
       <c r="AV14" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AW14" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AX14" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AY14" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AZ14" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BA14" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BB14" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BC14" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BD14" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BE14" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BF14" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BG14" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BH14" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BI14" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BJ14" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BK14" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BL14" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -4783,1063 +4783,1063 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>Physics 142; NIP R109</t>
+          <t>Physics 165; NIP R109</t>
         </is>
       </c>
       <c r="M15" s="5" t="inlineStr">
         <is>
-          <t>Physics 142; NIP R109</t>
+          <t>Physics 165; NIP R109</t>
         </is>
       </c>
       <c r="N15" s="5" t="inlineStr">
         <is>
-          <t>Physics 142; NIP R109</t>
+          <t>Physics 165; NIP R109</t>
         </is>
       </c>
       <c r="O15" s="5" t="inlineStr">
         <is>
-          <t>Physics 142; NIP R109</t>
+          <t>Physics 165; NIP R109</t>
         </is>
       </c>
       <c r="P15" s="5" t="inlineStr">
         <is>
-          <t>Physics 142; NIP R109</t>
+          <t>Physics 165; NIP R109</t>
         </is>
       </c>
       <c r="Q15" s="5" t="inlineStr">
         <is>
-          <t>Physics 142; NIP R109</t>
+          <t>Physics 165; NIP R109</t>
         </is>
       </c>
       <c r="R15" s="5" t="inlineStr">
         <is>
-          <t>Physics 170; NIP R201</t>
+          <t>PE 2 CH; TBA</t>
         </is>
       </c>
       <c r="S15" s="5" t="inlineStr">
         <is>
-          <t>Physics 170; NIP R201</t>
+          <t>PE 2 CH; TBA</t>
         </is>
       </c>
       <c r="T15" s="5" t="inlineStr">
         <is>
-          <t>Physics 170; NIP R201</t>
+          <t>PE 2 CH; TBA</t>
         </is>
       </c>
       <c r="U15" s="5" t="inlineStr">
         <is>
-          <t>Physics 170; NIP R201</t>
-        </is>
-      </c>
-      <c r="V15" s="5" t="inlineStr">
-        <is>
-          <t>Physics 170; NIP R201</t>
-        </is>
-      </c>
-      <c r="W15" s="5" t="inlineStr">
-        <is>
-          <t>Physics 170; NIP R201</t>
+          <t>PE 2 CH; TBA</t>
+        </is>
+      </c>
+      <c r="V15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="W15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="X15" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="Y15" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="Z15" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AA15" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AB15" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AC15" s="4" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AD15" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AE15" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AF15" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AG15" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AH15" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AI15" s="4" t="inlineStr">
-        <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AD15" s="5" t="inlineStr">
+        <is>
+          <t>App Physics 195; NIP F201</t>
+        </is>
+      </c>
+      <c r="AE15" s="5" t="inlineStr">
+        <is>
+          <t>App Physics 195; NIP F201</t>
+        </is>
+      </c>
+      <c r="AF15" s="5" t="inlineStr">
+        <is>
+          <t>App Physics 195; NIP F201</t>
+        </is>
+      </c>
+      <c r="AG15" s="5" t="inlineStr">
+        <is>
+          <t>App Physics 195; NIP F201</t>
+        </is>
+      </c>
+      <c r="AH15" s="5" t="inlineStr">
+        <is>
+          <t>App Physics 195; NIP F201</t>
+        </is>
+      </c>
+      <c r="AI15" s="5" t="inlineStr">
+        <is>
+          <t>App Physics 195; NIP F201</t>
         </is>
       </c>
       <c r="AJ15" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AK15" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AL15" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AM15" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AN15" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AO15" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AP15" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AQ15" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR15" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AS15" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AT15" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AU15" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AV15" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AW15" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AX15" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AY15" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AZ15" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BA15" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BB15" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BC15" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BD15" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BE15" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BF15" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BG15" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BH15" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BI15" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BJ15" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BK15" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BL15" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MARASIGAN, MIKE ANTHONY JOSON</t>
+          <t>LATAYAN, HEZEKIAH JULIAN ROCEF BARRIOS</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>Math 21; MARFIL, RI</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>Math 21; MARFIL, RI</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>Math 21; MARFIL, RI</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>Math 21; MARFIL, RI</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="M16" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="N16" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="O16" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="P16" s="4" t="inlineStr">
-        <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="M16" s="5" t="inlineStr">
+        <is>
+          <t>Physics 72; NIP F210</t>
+        </is>
+      </c>
+      <c r="N16" s="5" t="inlineStr">
+        <is>
+          <t>Physics 72; NIP F210</t>
+        </is>
+      </c>
+      <c r="O16" s="5" t="inlineStr">
+        <is>
+          <t>Physics 72; NIP F210</t>
+        </is>
+      </c>
+      <c r="P16" s="5" t="inlineStr">
+        <is>
+          <t>Physics 72; NIP F210</t>
         </is>
       </c>
       <c r="Q16" s="4" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="R16" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="S16" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="T16" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="U16" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="V16" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="W16" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="X16" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="Y16" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="Z16" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AA16" s="4" t="inlineStr">
-        <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="R16" s="5" t="inlineStr">
+        <is>
+          <t>EEE 121; EEEI 308</t>
+        </is>
+      </c>
+      <c r="S16" s="5" t="inlineStr">
+        <is>
+          <t>EEE 121; EEEI 308</t>
+        </is>
+      </c>
+      <c r="T16" s="5" t="inlineStr">
+        <is>
+          <t>EEE 121; EEEI 308</t>
+        </is>
+      </c>
+      <c r="U16" s="5" t="inlineStr">
+        <is>
+          <t>EEE 121; EEEI 308</t>
+        </is>
+      </c>
+      <c r="V16" s="5" t="inlineStr">
+        <is>
+          <t>EEE 121; EEEI 308</t>
+        </is>
+      </c>
+      <c r="W16" s="5" t="inlineStr">
+        <is>
+          <t>EEE 121; EEEI 308</t>
+        </is>
+      </c>
+      <c r="X16" s="5" t="inlineStr">
+        <is>
+          <t>EEE 121; EEEI 308</t>
+        </is>
+      </c>
+      <c r="Y16" s="5" t="inlineStr">
+        <is>
+          <t>EEE 121; EEEI 308</t>
+        </is>
+      </c>
+      <c r="Z16" s="5" t="inlineStr">
+        <is>
+          <t>EEE 121; EEEI 308</t>
+        </is>
+      </c>
+      <c r="AA16" s="5" t="inlineStr">
+        <is>
+          <t>EEE 121; EEEI 308</t>
         </is>
       </c>
       <c r="AB16" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AC16" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AD16" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE16" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AF16" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AG16" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AH16" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AI16" s="4" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AJ16" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AK16" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AL16" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AM16" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AN16" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AO16" s="4" t="inlineStr">
-        <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AJ16" s="5" t="inlineStr">
+        <is>
+          <t>EEE 123; EEEI 123</t>
+        </is>
+      </c>
+      <c r="AK16" s="5" t="inlineStr">
+        <is>
+          <t>EEE 123; EEEI 123</t>
+        </is>
+      </c>
+      <c r="AL16" s="5" t="inlineStr">
+        <is>
+          <t>EEE 123; EEEI 123</t>
+        </is>
+      </c>
+      <c r="AM16" s="5" t="inlineStr">
+        <is>
+          <t>EEE 123; EEEI 123</t>
+        </is>
+      </c>
+      <c r="AN16" s="5" t="inlineStr">
+        <is>
+          <t>EEE 123; EEEI 123</t>
+        </is>
+      </c>
+      <c r="AO16" s="5" t="inlineStr">
+        <is>
+          <t>EEE 123; EEEI 123</t>
         </is>
       </c>
       <c r="AP16" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AQ16" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR16" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AS16" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AT16" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AU16" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AV16" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AW16" s="4" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AX16" s="5" t="inlineStr">
-        <is>
-          <t>Law 103; LAW 221</t>
-        </is>
-      </c>
-      <c r="AY16" s="5" t="inlineStr">
-        <is>
-          <t>Law 103; LAW 221</t>
-        </is>
-      </c>
-      <c r="AZ16" s="5" t="inlineStr">
-        <is>
-          <t>Law 103; LAW 221</t>
-        </is>
-      </c>
-      <c r="BA16" s="5" t="inlineStr">
-        <is>
-          <t>Law 103; LAW 221</t>
-        </is>
-      </c>
-      <c r="BB16" s="5" t="inlineStr">
-        <is>
-          <t>Law 103; LAW 221</t>
-        </is>
-      </c>
-      <c r="BC16" s="5" t="inlineStr">
-        <is>
-          <t>Law 103; LAW 221</t>
-        </is>
-      </c>
-      <c r="BD16" s="5" t="inlineStr">
-        <is>
-          <t>Law 103; LAW 221</t>
-        </is>
-      </c>
-      <c r="BE16" s="5" t="inlineStr">
-        <is>
-          <t>Law 103; LAW 221</t>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AX16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AY16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AZ16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="BA16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="BB16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="BC16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="BD16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="BE16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BF16" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BG16" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BH16" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BI16" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BJ16" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BK16" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BL16" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PALESTROQUE, EARL MATTHEW ZALDARRIAGA</t>
+          <t>PASADILLA, JONAS AVRIL</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>Math 22; MB 307</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>Math 22; MB 307</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>Math 22; MB 307</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>Math 22; MB 307</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>Math 22; MB 307</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>Math 22; MB 307</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="M17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="N17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="O17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="P17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="M17" s="5" t="inlineStr">
+        <is>
+          <t>Physics 72; ORDONIO, AE</t>
+        </is>
+      </c>
+      <c r="N17" s="5" t="inlineStr">
+        <is>
+          <t>Physics 72; ORDONIO, AE</t>
+        </is>
+      </c>
+      <c r="O17" s="5" t="inlineStr">
+        <is>
+          <t>Physics 72; ORDONIO, AE</t>
+        </is>
+      </c>
+      <c r="P17" s="5" t="inlineStr">
+        <is>
+          <t>Physics 72; ORDONIO, AE</t>
         </is>
       </c>
       <c r="Q17" s="4" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="R17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="S17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="T17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="U17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="V17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="W17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="X17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="Y17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="Z17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AA17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AB17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AC17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AD17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AE17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AF17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AG17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AH17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AI17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AJ17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AK17" s="4" t="inlineStr">
-        <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="R17" s="5" t="inlineStr">
+        <is>
+          <t>ChemE 102; lab A402</t>
+        </is>
+      </c>
+      <c r="S17" s="5" t="inlineStr">
+        <is>
+          <t>ChemE 102; lab A402</t>
+        </is>
+      </c>
+      <c r="T17" s="5" t="inlineStr">
+        <is>
+          <t>ChemE 102; lab A402</t>
+        </is>
+      </c>
+      <c r="U17" s="5" t="inlineStr">
+        <is>
+          <t>ChemE 102; lab A402</t>
+        </is>
+      </c>
+      <c r="V17" s="5" t="inlineStr">
+        <is>
+          <t>ChemE 102; lab A402</t>
+        </is>
+      </c>
+      <c r="W17" s="5" t="inlineStr">
+        <is>
+          <t>ChemE 102; lab A402</t>
+        </is>
+      </c>
+      <c r="X17" s="5" t="inlineStr">
+        <is>
+          <t>ChemE 102; lab A402</t>
+        </is>
+      </c>
+      <c r="Y17" s="5" t="inlineStr">
+        <is>
+          <t>ChemE 102; lab A402</t>
+        </is>
+      </c>
+      <c r="Z17" s="5" t="inlineStr">
+        <is>
+          <t>ChemE 102; lab A402</t>
+        </is>
+      </c>
+      <c r="AA17" s="5" t="inlineStr">
+        <is>
+          <t>ChemE 102; lab A402</t>
+        </is>
+      </c>
+      <c r="AB17" s="5" t="inlineStr">
+        <is>
+          <t>ChemE 102; lab A402</t>
+        </is>
+      </c>
+      <c r="AC17" s="5" t="inlineStr">
+        <is>
+          <t>ChemE 102; lab A402</t>
+        </is>
+      </c>
+      <c r="AD17" s="5" t="inlineStr">
+        <is>
+          <t>ChemE 105; lec A302</t>
+        </is>
+      </c>
+      <c r="AE17" s="5" t="inlineStr">
+        <is>
+          <t>ChemE 105; lec A302</t>
+        </is>
+      </c>
+      <c r="AF17" s="5" t="inlineStr">
+        <is>
+          <t>ChemE 105; lec A302</t>
+        </is>
+      </c>
+      <c r="AG17" s="5" t="inlineStr">
+        <is>
+          <t>ChemE 105; lec A302</t>
+        </is>
+      </c>
+      <c r="AH17" s="5" t="inlineStr">
+        <is>
+          <t>ChemE 105; lec A302</t>
+        </is>
+      </c>
+      <c r="AI17" s="5" t="inlineStr">
+        <is>
+          <t>ChemE 105; lec A302</t>
+        </is>
+      </c>
+      <c r="AJ17" s="5" t="inlineStr">
+        <is>
+          <t>ChemE 105; lec A302</t>
+        </is>
+      </c>
+      <c r="AK17" s="5" t="inlineStr">
+        <is>
+          <t>ChemE 105; lec A302</t>
         </is>
       </c>
       <c r="AL17" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AM17" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AN17" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AO17" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AP17" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AQ17" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR17" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AS17" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AT17" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AU17" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AV17" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AW17" s="4" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AX17" s="5" t="inlineStr">
-        <is>
-          <t>Law 113; LAW 307-309</t>
-        </is>
-      </c>
-      <c r="AY17" s="5" t="inlineStr">
-        <is>
-          <t>Law 113; LAW 307-309</t>
-        </is>
-      </c>
-      <c r="AZ17" s="5" t="inlineStr">
-        <is>
-          <t>Law 113; LAW 307-309</t>
-        </is>
-      </c>
-      <c r="BA17" s="5" t="inlineStr">
-        <is>
-          <t>Law 113; LAW 307-309</t>
-        </is>
-      </c>
-      <c r="BB17" s="5" t="inlineStr">
-        <is>
-          <t>Law 113; LAW 307-309</t>
-        </is>
-      </c>
-      <c r="BC17" s="5" t="inlineStr">
-        <is>
-          <t>Law 113; LAW 307-309</t>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AX17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AY17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AZ17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="BA17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="BB17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="BC17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BD17" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BE17" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BF17" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BG17" s="4" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="BH17" s="5" t="inlineStr">
-        <is>
-          <t>Law 105; LAW 307-309</t>
-        </is>
-      </c>
-      <c r="BI17" s="5" t="inlineStr">
-        <is>
-          <t>Law 105; LAW 307-309</t>
-        </is>
-      </c>
-      <c r="BJ17" s="5" t="inlineStr">
-        <is>
-          <t>Law 105; LAW 307-309</t>
-        </is>
-      </c>
-      <c r="BK17" s="5" t="inlineStr">
-        <is>
-          <t>Law 105; LAW 307-309</t>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="BH17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="BI17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="BJ17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="BK17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BL17" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PANTOJA, JANWIN MYL ROMERO</t>
+          <t>TAYO, MARCUS JAMES REMO</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>Physics 72; NIP F210</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>Physics 72; NIP F210</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>Physics 72; NIP F210</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>Physics 72; NIP F210</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="L18" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="M18" s="4" t="inlineStr">
-        <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>Math 22; MB 304</t>
+        </is>
+      </c>
+      <c r="M18" s="5" t="inlineStr">
+        <is>
+          <t>Math 22; MB 304</t>
         </is>
       </c>
       <c r="N18" s="5" t="inlineStr">
         <is>
-          <t>Math 23; TBA</t>
+          <t>Math 22; MB 304</t>
         </is>
       </c>
       <c r="O18" s="5" t="inlineStr">
         <is>
-          <t>Math 23; TBA</t>
+          <t>Math 22; MB 304</t>
         </is>
       </c>
       <c r="P18" s="5" t="inlineStr">
         <is>
-          <t>Math 23; TBA</t>
+          <t>Math 22; MB 304</t>
         </is>
       </c>
       <c r="Q18" s="5" t="inlineStr">
         <is>
-          <t>Math 23; TBA</t>
+          <t>Math 22; MB 304</t>
         </is>
       </c>
       <c r="R18" s="5" t="inlineStr">
@@ -5874,1193 +5874,539 @@
       </c>
       <c r="X18" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="Y18" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="Z18" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AA18" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AB18" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AC18" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AD18" s="5" t="inlineStr">
         <is>
-          <t>EEE 133; EEEI 421</t>
+          <t>ARTS 1; PH 217</t>
         </is>
       </c>
       <c r="AE18" s="5" t="inlineStr">
         <is>
-          <t>EEE 133; EEEI 421</t>
+          <t>ARTS 1; PH 217</t>
         </is>
       </c>
       <c r="AF18" s="5" t="inlineStr">
         <is>
-          <t>EEE 133; EEEI 421</t>
+          <t>ARTS 1; PH 217</t>
         </is>
       </c>
       <c r="AG18" s="5" t="inlineStr">
         <is>
-          <t>EEE 133; EEEI 421</t>
+          <t>ARTS 1; PH 217</t>
         </is>
       </c>
       <c r="AH18" s="5" t="inlineStr">
         <is>
-          <t>EEE 133; EEEI 421</t>
+          <t>ARTS 1; PH 217</t>
         </is>
       </c>
       <c r="AI18" s="5" t="inlineStr">
         <is>
-          <t>EEE 133; EEEI 421</t>
-        </is>
-      </c>
-      <c r="AJ18" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AK18" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AL18" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AM18" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AN18" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AO18" s="4" t="inlineStr">
-        <is>
-          <t> </t>
+          <t>ARTS 1; PH 217</t>
+        </is>
+      </c>
+      <c r="AJ18" s="5" t="inlineStr">
+        <is>
+          <t>EEE 123; EEEI 420</t>
+        </is>
+      </c>
+      <c r="AK18" s="5" t="inlineStr">
+        <is>
+          <t>EEE 123; EEEI 420</t>
+        </is>
+      </c>
+      <c r="AL18" s="5" t="inlineStr">
+        <is>
+          <t>EEE 123; EEEI 420</t>
+        </is>
+      </c>
+      <c r="AM18" s="5" t="inlineStr">
+        <is>
+          <t>EEE 123; EEEI 420</t>
+        </is>
+      </c>
+      <c r="AN18" s="5" t="inlineStr">
+        <is>
+          <t>EEE 123; EEEI 420</t>
+        </is>
+      </c>
+      <c r="AO18" s="5" t="inlineStr">
+        <is>
+          <t>EEE 123; EEEI 420</t>
         </is>
       </c>
       <c r="AP18" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AQ18" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR18" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AS18" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AT18" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AU18" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AV18" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AW18" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AX18" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AY18" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AZ18" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BA18" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BB18" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BC18" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BD18" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BE18" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BF18" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BG18" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BH18" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BI18" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BJ18" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BK18" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BL18" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BM18" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PASADILLA, JONAS AVRIL</t>
+          <t>VELDA, ADAM RISH CAIYOD</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>Math 21; MB 306</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>Math 21; MB 306</t>
-        </is>
-      </c>
-      <c r="I19" s="5" t="inlineStr">
-        <is>
-          <t>Math 21; MB 306</t>
-        </is>
-      </c>
-      <c r="J19" s="5" t="inlineStr">
-        <is>
-          <t>Math 21; MB 306</t>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="L19" s="5" t="inlineStr">
-        <is>
-          <t>Eng 13; CAL 310</t>
-        </is>
-      </c>
-      <c r="M19" s="5" t="inlineStr">
-        <is>
-          <t>Eng 13; CAL 310</t>
-        </is>
-      </c>
-      <c r="N19" s="5" t="inlineStr">
-        <is>
-          <t>Eng 13; CAL 310</t>
-        </is>
-      </c>
-      <c r="O19" s="5" t="inlineStr">
-        <is>
-          <t>Eng 13; CAL 310</t>
-        </is>
-      </c>
-      <c r="P19" s="5" t="inlineStr">
-        <is>
-          <t>Eng 13; CAL 310</t>
-        </is>
-      </c>
-      <c r="Q19" s="5" t="inlineStr">
-        <is>
-          <t>Eng 13; CAL 310</t>
-        </is>
-      </c>
-      <c r="R19" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="S19" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="T19" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="U19" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="V19" s="4" t="inlineStr">
-        <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="M19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="N19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="O19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="P19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="Q19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="R19" s="5" t="inlineStr">
+        <is>
+          <t>Physics 108; NIP LP103</t>
+        </is>
+      </c>
+      <c r="S19" s="5" t="inlineStr">
+        <is>
+          <t>Physics 108; NIP LP103</t>
+        </is>
+      </c>
+      <c r="T19" s="5" t="inlineStr">
+        <is>
+          <t>Physics 108; NIP LP103</t>
+        </is>
+      </c>
+      <c r="U19" s="5" t="inlineStr">
+        <is>
+          <t>Physics 108; NIP LP103</t>
+        </is>
+      </c>
+      <c r="V19" s="5" t="inlineStr">
+        <is>
+          <t>Physics 108; NIP LP103</t>
         </is>
       </c>
       <c r="W19" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="X19" s="5" t="inlineStr">
         <is>
-          <t>ChemE 101; MH 321</t>
+          <t>App Physics 155; NIP LP103</t>
         </is>
       </c>
       <c r="Y19" s="5" t="inlineStr">
         <is>
-          <t>ChemE 101; MH 321</t>
+          <t>App Physics 155; NIP LP103</t>
         </is>
       </c>
       <c r="Z19" s="5" t="inlineStr">
         <is>
-          <t>ChemE 101; MH 321</t>
+          <t>App Physics 155; NIP LP103</t>
         </is>
       </c>
       <c r="AA19" s="5" t="inlineStr">
         <is>
-          <t>ChemE 101; MH 321</t>
+          <t>App Physics 155; NIP LP103</t>
         </is>
       </c>
       <c r="AB19" s="5" t="inlineStr">
         <is>
-          <t>ChemE 101; MH 321</t>
+          <t>App Physics 155; NIP LP103</t>
         </is>
       </c>
       <c r="AC19" s="5" t="inlineStr">
         <is>
-          <t>ChemE 101; MH 321</t>
-        </is>
-      </c>
-      <c r="AD19" s="5" t="inlineStr">
-        <is>
-          <t>ChemE 101; MH 321</t>
-        </is>
-      </c>
-      <c r="AE19" s="5" t="inlineStr">
-        <is>
-          <t>ChemE 101; MH 321</t>
-        </is>
-      </c>
-      <c r="AF19" s="5" t="inlineStr">
-        <is>
-          <t>ChemE 101; MH 321</t>
-        </is>
-      </c>
-      <c r="AG19" s="5" t="inlineStr">
-        <is>
-          <t>ChemE 101; MH 321</t>
-        </is>
-      </c>
-      <c r="AH19" s="5" t="inlineStr">
-        <is>
-          <t>ChemE 101; MH 321</t>
-        </is>
-      </c>
-      <c r="AI19" s="5" t="inlineStr">
-        <is>
-          <t>ChemE 101; MH 321</t>
-        </is>
-      </c>
-      <c r="AJ19" s="5" t="inlineStr">
-        <is>
-          <t>Physics 71; NIP F203</t>
-        </is>
-      </c>
-      <c r="AK19" s="5" t="inlineStr">
-        <is>
-          <t>Physics 71; NIP F203</t>
-        </is>
-      </c>
-      <c r="AL19" s="5" t="inlineStr">
-        <is>
-          <t>Physics 71; NIP F203</t>
-        </is>
-      </c>
-      <c r="AM19" s="5" t="inlineStr">
-        <is>
-          <t>Physics 71; NIP F203</t>
-        </is>
-      </c>
-      <c r="AN19" s="5" t="inlineStr">
-        <is>
-          <t>Physics 71; NIP F203</t>
-        </is>
-      </c>
-      <c r="AO19" s="5" t="inlineStr">
-        <is>
-          <t>Physics 71; NIP F203</t>
+          <t>App Physics 155; NIP LP103</t>
+        </is>
+      </c>
+      <c r="AD19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AE19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AF19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AG19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AH19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AI19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AJ19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AK19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AL19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AM19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AN19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AO19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AP19" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AQ19" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR19" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AS19" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AT19" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AU19" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AV19" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AW19" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AX19" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AY19" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AZ19" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BA19" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BB19" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BC19" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BD19" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BE19" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BF19" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BG19" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BH19" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BI19" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BJ19" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BK19" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BL19" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="BM19" s="4" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>TAYO, MARCUS JAMES REMO</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>Physics 71; NIP F209</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>Physics 71; NIP F209</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>Physics 71; NIP F209</t>
-        </is>
-      </c>
-      <c r="I20" s="5" t="inlineStr">
-        <is>
-          <t>Physics 71; NIP F209</t>
-        </is>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="L20" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="M20" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="N20" s="5" t="inlineStr">
-        <is>
-          <t>PE 2 RF; TBA</t>
-        </is>
-      </c>
-      <c r="O20" s="5" t="inlineStr">
-        <is>
-          <t>PE 2 RF; TBA</t>
-        </is>
-      </c>
-      <c r="P20" s="5" t="inlineStr">
-        <is>
-          <t>PE 2 RF; TBA</t>
-        </is>
-      </c>
-      <c r="Q20" s="5" t="inlineStr">
-        <is>
-          <t>PE 2 RF; TBA</t>
-        </is>
-      </c>
-      <c r="R20" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="S20" s="5" t="inlineStr">
-        <is>
-          <t>Math 21; MB 304</t>
-        </is>
-      </c>
-      <c r="T20" s="5" t="inlineStr">
-        <is>
-          <t>Math 21; MB 304</t>
-        </is>
-      </c>
-      <c r="U20" s="5" t="inlineStr">
-        <is>
-          <t>Math 21; MB 304</t>
-        </is>
-      </c>
-      <c r="V20" s="5" t="inlineStr">
-        <is>
-          <t>Math 21; MB 304</t>
-        </is>
-      </c>
-      <c r="W20" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="X20" s="5" t="inlineStr">
-        <is>
-          <t>EEE 111; EEEI 204</t>
-        </is>
-      </c>
-      <c r="Y20" s="5" t="inlineStr">
-        <is>
-          <t>EEE 111; EEEI 204</t>
-        </is>
-      </c>
-      <c r="Z20" s="5" t="inlineStr">
-        <is>
-          <t>EEE 111; EEEI 204</t>
-        </is>
-      </c>
-      <c r="AA20" s="5" t="inlineStr">
-        <is>
-          <t>EEE 111; EEEI 204</t>
-        </is>
-      </c>
-      <c r="AB20" s="5" t="inlineStr">
-        <is>
-          <t>EEE 111; EEEI 204</t>
-        </is>
-      </c>
-      <c r="AC20" s="5" t="inlineStr">
-        <is>
-          <t>EEE 111; EEEI 204</t>
-        </is>
-      </c>
-      <c r="AD20" s="5" t="inlineStr">
-        <is>
-          <t>EEE 111; EEEI 204</t>
-        </is>
-      </c>
-      <c r="AE20" s="5" t="inlineStr">
-        <is>
-          <t>EEE 111; EEEI 204</t>
-        </is>
-      </c>
-      <c r="AF20" s="5" t="inlineStr">
-        <is>
-          <t>EEE 111; EEEI 204</t>
-        </is>
-      </c>
-      <c r="AG20" s="5" t="inlineStr">
-        <is>
-          <t>EEE 111; EEEI 204</t>
-        </is>
-      </c>
-      <c r="AH20" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AI20" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AJ20" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AK20" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AL20" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AM20" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AN20" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AO20" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AP20" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AQ20" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AR20" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AS20" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AT20" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AU20" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AV20" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AW20" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AX20" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AY20" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AZ20" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="BA20" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="BB20" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="BC20" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="BD20" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="BE20" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="BF20" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="BG20" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="BH20" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="BI20" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="BJ20" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="BK20" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="BL20" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="BM20" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>VELDA, ADAM RISH CAIYOD</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="L21" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="M21" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="N21" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="O21" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="P21" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="Q21" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="R21" s="5" t="inlineStr">
-        <is>
-          <t>Physics 108; NIP LP103</t>
-        </is>
-      </c>
-      <c r="S21" s="5" t="inlineStr">
-        <is>
-          <t>Physics 108; NIP LP103</t>
-        </is>
-      </c>
-      <c r="T21" s="5" t="inlineStr">
-        <is>
-          <t>Physics 108; NIP LP103</t>
-        </is>
-      </c>
-      <c r="U21" s="5" t="inlineStr">
-        <is>
-          <t>Physics 108; NIP LP103</t>
-        </is>
-      </c>
-      <c r="V21" s="5" t="inlineStr">
-        <is>
-          <t>Physics 108; NIP LP103</t>
-        </is>
-      </c>
-      <c r="W21" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="X21" s="5" t="inlineStr">
-        <is>
-          <t>App Physics 155; NIP LP103</t>
-        </is>
-      </c>
-      <c r="Y21" s="5" t="inlineStr">
-        <is>
-          <t>App Physics 155; NIP LP103</t>
-        </is>
-      </c>
-      <c r="Z21" s="5" t="inlineStr">
-        <is>
-          <t>App Physics 155; NIP LP103</t>
-        </is>
-      </c>
-      <c r="AA21" s="5" t="inlineStr">
-        <is>
-          <t>App Physics 155; NIP LP103</t>
-        </is>
-      </c>
-      <c r="AB21" s="5" t="inlineStr">
-        <is>
-          <t>App Physics 155; NIP LP103</t>
-        </is>
-      </c>
-      <c r="AC21" s="5" t="inlineStr">
-        <is>
-          <t>App Physics 155; NIP LP103</t>
-        </is>
-      </c>
-      <c r="AD21" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AE21" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AF21" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AG21" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AH21" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AI21" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AJ21" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AK21" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AL21" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AM21" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AN21" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AO21" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AP21" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AQ21" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AR21" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AS21" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AT21" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AU21" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AV21" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AW21" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AX21" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AY21" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="AZ21" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="BA21" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="BB21" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="BC21" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="BD21" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="BE21" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="BF21" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="BG21" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="BH21" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="BI21" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="BJ21" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="BK21" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="BL21" s="4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="BM21" s="4" t="inlineStr">
-        <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
